--- a/Excel/car inventory.xlsx
+++ b/Excel/car inventory.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\j-l-data-science-data-analytics\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tests\j-l-data-science-data-analytics\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9258AC24-450D-42FD-979D-3BC647337D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB915F5-6497-48D7-AF85-94076CAE0544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{6F1C8A56-E294-480C-BFA2-897A20BA14D1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F1C8A56-E294-480C-BFA2-897A20BA14D1}"/>
   </bookViews>
   <sheets>
     <sheet name="car inventory" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'car inventory'!$1:$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -963,17 +979,7 @@
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -986,11 +992,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1008,9 +1014,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1048,7 +1054,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1154,7 +1160,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1296,7 +1302,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1304,23 +1310,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1BE64A-6E35-46AF-B538-7FFA7D2A357E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="7"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="7"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" style="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1364,7 +1373,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
@@ -1417,7 +1426,7 @@
         <v>FD06MTGBLA001</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
@@ -1470,7 +1479,7 @@
         <v>FD06MTGWHI002</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
@@ -1523,7 +1532,7 @@
         <v>FD08MTGGRE003</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>23</v>
       </c>
@@ -1576,7 +1585,7 @@
         <v>FD08MTGBLA004</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>25</v>
       </c>
@@ -1629,7 +1638,7 @@
         <v>FD08MTGWHI005</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>119</v>
       </c>
@@ -1682,7 +1691,7 @@
         <v>FD06FCSGRE006</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>27</v>
       </c>
@@ -1735,7 +1744,7 @@
         <v>FD06FCSGRE007</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>28</v>
       </c>
@@ -1788,7 +1797,7 @@
         <v>FD09FCSBLA008</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>30</v>
       </c>
@@ -1841,7 +1850,7 @@
         <v>FD13FCSBLA009</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>31</v>
       </c>
@@ -1894,7 +1903,7 @@
         <v>FD13FCSWHI010</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>33</v>
       </c>
@@ -1947,7 +1956,7 @@
         <v>FD12FCSWHI011</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>35</v>
       </c>
@@ -2000,7 +2009,7 @@
         <v>FD13FCSBLA012</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
@@ -2053,7 +2062,7 @@
         <v>FD13FCSBLA013</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>120</v>
       </c>
@@ -2106,7 +2115,7 @@
         <v>GM09CMRWHI014</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
@@ -2159,7 +2168,7 @@
         <v>GM12CMRBLA015</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>42</v>
       </c>
@@ -2212,7 +2221,7 @@
         <v>GM14CMRWHI016</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>44</v>
       </c>
@@ -2265,7 +2274,7 @@
         <v>GM10SLVBLA017</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>46</v>
       </c>
@@ -2318,7 +2327,7 @@
         <v>GM98SLVBLA018</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>47</v>
       </c>
@@ -2371,7 +2380,7 @@
         <v>GM00SLVBLU019</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>49</v>
       </c>
@@ -2424,7 +2433,7 @@
         <v>TY96CAMGRE020</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>51</v>
       </c>
@@ -2477,7 +2486,7 @@
         <v>TY98CAMBLA021</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>53</v>
       </c>
@@ -2530,7 +2539,7 @@
         <v>TY00CAMGRE022</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>54</v>
       </c>
@@ -2583,7 +2592,7 @@
         <v>TY02CAMBLA023</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>55</v>
       </c>
@@ -2636,7 +2645,7 @@
         <v>TY09CAMWHI024</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>56</v>
       </c>
@@ -2689,7 +2698,7 @@
         <v>TY02CORRED025</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>59</v>
       </c>
@@ -2742,7 +2751,7 @@
         <v>TY03CORBLA026</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>60</v>
       </c>
@@ -2795,7 +2804,7 @@
         <v>TY14CORBLU027</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>61</v>
       </c>
@@ -2848,7 +2857,7 @@
         <v>TY12CORBLA028</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>62</v>
       </c>
@@ -2901,7 +2910,7 @@
         <v>TY12CAMBLU029</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>63</v>
       </c>
@@ -2954,7 +2963,7 @@
         <v>HO99CIVWHI030</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>64</v>
       </c>
@@ -3007,7 +3016,7 @@
         <v>HO01CIVBLU031</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>65</v>
       </c>
@@ -3060,7 +3069,7 @@
         <v>HO10CIVBLU032</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>66</v>
       </c>
@@ -3113,7 +3122,7 @@
         <v>HO10CIVBLA033</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>67</v>
       </c>
@@ -3166,7 +3175,7 @@
         <v>HO11CIVBLA034</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>68</v>
       </c>
@@ -3219,7 +3228,7 @@
         <v>HO12CIVBLA035</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>69</v>
       </c>
@@ -3272,7 +3281,7 @@
         <v>HO13CIVBLA036</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>121</v>
       </c>
@@ -3325,7 +3334,7 @@
         <v>HO05ODYWHI037</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>70</v>
       </c>
@@ -3378,7 +3387,7 @@
         <v>HO07ODYBLA038</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>71</v>
       </c>
@@ -3431,7 +3440,7 @@
         <v>HO08ODYWHI039</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>118</v>
       </c>
@@ -3484,7 +3493,7 @@
         <v>HO01ODYBLA040</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>72</v>
       </c>
@@ -3537,7 +3546,7 @@
         <v>HO14ODYBLA041</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>73</v>
       </c>
@@ -3590,7 +3599,7 @@
         <v>CR04PTCBLU042</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>74</v>
       </c>
@@ -3643,7 +3652,7 @@
         <v>CR07PTCGRE043</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>75</v>
       </c>
@@ -3696,7 +3705,7 @@
         <v>CR11PTCBLA044</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>76</v>
       </c>
@@ -3749,7 +3758,7 @@
         <v>CR99CARGRE045</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>77</v>
       </c>
@@ -3802,7 +3811,7 @@
         <v>CR00CARBLA046</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>78</v>
       </c>
@@ -3855,7 +3864,7 @@
         <v>CR04CARWHI047</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>79</v>
       </c>
@@ -3908,7 +3917,7 @@
         <v>CR04CARRED048</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>80</v>
       </c>
@@ -3961,7 +3970,7 @@
         <v>HY11ELABLA049</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>81</v>
       </c>
@@ -4014,7 +4023,7 @@
         <v>HY12ELABLU050</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>82</v>
       </c>
@@ -4067,7 +4076,7 @@
         <v>HY13ELABLA051</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>83</v>
       </c>
@@ -4120,7 +4129,7 @@
         <v>HY13ELABLU052</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
         <v>84</v>
       </c>
@@ -4134,7 +4143,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
         <v>89</v>
       </c>
@@ -4148,7 +4157,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B59" s="7" t="s">
         <v>88</v>
       </c>
@@ -4162,7 +4171,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
         <v>87</v>
       </c>
@@ -4176,7 +4185,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B61" s="7" t="s">
         <v>85</v>
       </c>
@@ -4190,7 +4199,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B62" s="7" t="s">
         <v>86</v>
       </c>
@@ -4204,7 +4213,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D63" s="4" t="s">
         <v>100</v>
       </c>
@@ -4212,7 +4221,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D64" s="4" t="s">
         <v>110</v>
       </c>
@@ -4220,7 +4229,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="65" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D65" s="4" t="s">
         <v>112</v>
       </c>
@@ -4228,7 +4237,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="66" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D66" s="4" t="s">
         <v>114</v>
       </c>
@@ -4236,7 +4245,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="67" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D67" s="4" t="s">
         <v>116</v>
       </c>
@@ -4245,18 +4254,18 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D57:E67">
-    <sortCondition ref="D57:D67"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B57:C62">
+    <sortCondition ref="B57:B62"/>
   </sortState>
   <conditionalFormatting sqref="M2:M53">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Not Covered"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"Y"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"Not Covered"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="79" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/car inventory.xlsx
+++ b/Excel/car inventory.xlsx
@@ -8,17 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tests\j-l-data-science-data-analytics\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB915F5-6497-48D7-AF85-94076CAE0544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1E596D-049E-4D2F-B185-083CC6FAC426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F1C8A56-E294-480C-BFA2-897A20BA14D1}"/>
   </bookViews>
   <sheets>
-    <sheet name="car inventory" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="car inventory" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'car inventory'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'car inventory'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'car inventory'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="3" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="125">
   <si>
     <t>Car ID</t>
   </si>
@@ -402,6 +407,15 @@
   </si>
   <si>
     <t>HO05ODY037</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Miles</t>
   </si>
 </sst>
 </file>
@@ -904,7 +918,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -933,6 +947,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -979,7 +998,27 @@
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1011,6 +1050,3578 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[car inventory.xlsx]Sheet1!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d contourW="9525">
+            <a:contourClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="0"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="60"/>
+      <c:rAngAx val="0"/>
+      <c:perspective val="100"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d contourW="9525">
+              <a:contourClr>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:contourClr>
+            </a:sp3d>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>Bard</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Chan</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Ewenty</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Gaul</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Howard</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hulinski</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jones</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Lyon</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>McCall</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Praulty</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Rodriguez</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Santos</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Smith</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Swartz</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Torrens</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Vizzini</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Yousef</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$4:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>144647.69999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>150656.40000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>154427.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>179986</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>143640.70000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>135078.20000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>184693.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>127731.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70964.899999999994</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>65315</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>138561.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>141229.4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>305432.40000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>177713.9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>65964.899999999994</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>130601.59999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19341.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-ECB3-4626-A318-6635DA2856DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="65"/>
+        <c:shape val="box"/>
+        <c:axId val="1165745887"/>
+        <c:axId val="1150556015"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="1165745887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1150556015"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1150556015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1165745887"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Miles &amp; Ages</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'car inventory'!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Miles</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'car inventory'!$G$2:$G$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="66"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'car inventory'!$H$2:$H$67</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="66"/>
+                <c:pt idx="0">
+                  <c:v>3708.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13682.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13867.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14289.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17556.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19341.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19421.099999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20223.900000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22128.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22188.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22282</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22521.599999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>22573</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>24513.200000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>27394.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>27534.799999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>27637.1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>28464.799999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>29102.3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>29601.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>30555.3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>31144.400000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>33477.199999999997</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>35137</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>36438.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>37558.800000000003</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>40326.800000000003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>42074.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>42504.6</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>44946.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>44974.8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46311.4</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>48114.2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>50854.1</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>52229.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>52699.4</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>60389.5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>64467.4</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>64542</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>67829.100000000006</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>68658.899999999994</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>69891.899999999994</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>72527.199999999997</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>73444.399999999994</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>77243.100000000006</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>79420.600000000006</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>80685.8</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>82374</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>83162.7</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>85928</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>93382.6</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>114660.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-931A-4499-ACFC-5BDF7BDD98D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1272200111"/>
+        <c:axId val="1150556975"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1272200111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Age</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> of the Car (Years)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1150556975"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1150556975"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Miles Driven</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1272200111"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="288">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:sp3d/>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr/>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>487680</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29037251-8CB7-7CE6-1683-48A376044CAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{971A774D-A3D8-B394-D771-9F2A2B70995C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="VICTUS" refreshedDate="46326.73575428241" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="52" xr:uid="{EF336E3D-25B8-4B4C-8D37-63CD18F0AC71}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:N53" sheet="car inventory"/>
+  </cacheSource>
+  <cacheFields count="14">
+    <cacheField name="Car ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Make" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Make (Full Name)" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Model" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Model (Full Name)" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Manufacture Year" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Age" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="12" maxValue="30"/>
+    </cacheField>
+    <cacheField name="Miles" numFmtId="43">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3708.1" maxValue="114660.6"/>
+    </cacheField>
+    <cacheField name="Miles / Year" numFmtId="43">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="309.00833333333333" maxValue="3822.02"/>
+    </cacheField>
+    <cacheField name="Color" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Driver" numFmtId="0">
+      <sharedItems count="17">
+        <s v="Smith"/>
+        <s v="McCall"/>
+        <s v="Lyon"/>
+        <s v="Jones"/>
+        <s v="Ewenty"/>
+        <s v="Howard"/>
+        <s v="Praulty"/>
+        <s v="Yousef"/>
+        <s v="Vizzini"/>
+        <s v="Rodriguez"/>
+        <s v="Santos"/>
+        <s v="Bard"/>
+        <s v="Torrens"/>
+        <s v="Hulinski"/>
+        <s v="Chan"/>
+        <s v="Swartz"/>
+        <s v="Gaul"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Warantee Miles" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50000" maxValue="100000"/>
+    </cacheField>
+    <cacheField name="Covered?" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="New Car ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="52">
+  <r>
+    <s v="FD06MTG001"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="MTG"/>
+    <s v="Mustag"/>
+    <s v="06"/>
+    <n v="20"/>
+    <n v="40326.800000000003"/>
+    <n v="2016.3400000000001"/>
+    <s v="Black"/>
+    <x v="0"/>
+    <n v="50000"/>
+    <s v="Y"/>
+    <s v="FD06MTGBLA001"/>
+  </r>
+  <r>
+    <s v="FD06MTG002"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="MTG"/>
+    <s v="Mustag"/>
+    <s v="06"/>
+    <n v="20"/>
+    <n v="44974.8"/>
+    <n v="2248.7400000000002"/>
+    <s v="White"/>
+    <x v="1"/>
+    <n v="50000"/>
+    <s v="Y"/>
+    <s v="FD06MTGWHI002"/>
+  </r>
+  <r>
+    <s v="FD08MTG003"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="MTG"/>
+    <s v="Mustag"/>
+    <s v="08"/>
+    <n v="18"/>
+    <n v="44946.5"/>
+    <n v="2497.0277777777778"/>
+    <s v="Green"/>
+    <x v="2"/>
+    <n v="50000"/>
+    <s v="Y"/>
+    <s v="FD08MTGGRE003"/>
+  </r>
+  <r>
+    <s v="FD08MTG004"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="MTG"/>
+    <s v="Mustag"/>
+    <s v="08"/>
+    <n v="18"/>
+    <n v="37558.800000000003"/>
+    <n v="2086.6000000000004"/>
+    <s v="Black"/>
+    <x v="3"/>
+    <n v="50000"/>
+    <s v="Y"/>
+    <s v="FD08MTGBLA004"/>
+  </r>
+  <r>
+    <s v="FD08MTG005"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="MTG"/>
+    <s v="Mustag"/>
+    <s v="08"/>
+    <n v="18"/>
+    <n v="36438.5"/>
+    <n v="2024.3611111111111"/>
+    <s v="White"/>
+    <x v="0"/>
+    <n v="50000"/>
+    <s v="Y"/>
+    <s v="FD08MTGWHI005"/>
+  </r>
+  <r>
+    <s v="FD06FCS006"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="FCS"/>
+    <s v="Focus"/>
+    <s v="06"/>
+    <n v="20"/>
+    <n v="46311.4"/>
+    <n v="2315.5700000000002"/>
+    <s v="Green"/>
+    <x v="4"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="FD06FCSGRE006"/>
+  </r>
+  <r>
+    <s v="FD06FCS007"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="FCS"/>
+    <s v="Focus"/>
+    <s v="06"/>
+    <n v="20"/>
+    <n v="52229.5"/>
+    <n v="2611.4749999999999"/>
+    <s v="Green"/>
+    <x v="2"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="FD06FCSGRE007"/>
+  </r>
+  <r>
+    <s v="FD09FCS008"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="FCS"/>
+    <s v="Focus"/>
+    <s v="09"/>
+    <n v="17"/>
+    <n v="35137"/>
+    <n v="2066.8823529411766"/>
+    <s v="Black"/>
+    <x v="5"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="FD09FCSBLA008"/>
+  </r>
+  <r>
+    <s v="FD13FCS009"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="FCS"/>
+    <s v="Focus"/>
+    <s v="13"/>
+    <n v="13"/>
+    <n v="27637.1"/>
+    <n v="2125.9307692307693"/>
+    <s v="Black"/>
+    <x v="0"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="FD13FCSBLA009"/>
+  </r>
+  <r>
+    <s v="FD13FCS010"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="FCS"/>
+    <s v="Focus"/>
+    <s v="13"/>
+    <n v="13"/>
+    <n v="27534.799999999999"/>
+    <n v="2118.0615384615385"/>
+    <s v="White"/>
+    <x v="6"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="FD13FCSWHI010"/>
+  </r>
+  <r>
+    <s v="FD12FCS011"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="FCS"/>
+    <s v="Focus"/>
+    <s v="12"/>
+    <n v="14"/>
+    <n v="19341.7"/>
+    <n v="1381.55"/>
+    <s v="White"/>
+    <x v="7"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="FD12FCSWHI011"/>
+  </r>
+  <r>
+    <s v="FD13FCS012"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="FCS"/>
+    <s v="Focus"/>
+    <s v="13"/>
+    <n v="13"/>
+    <n v="22521.599999999999"/>
+    <n v="1732.4307692307691"/>
+    <s v="Black"/>
+    <x v="8"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="FD13FCSBLA012"/>
+  </r>
+  <r>
+    <s v="FD13FCS013"/>
+    <s v="FD"/>
+    <s v="Ford"/>
+    <s v="FCS"/>
+    <s v="Focus"/>
+    <s v="13"/>
+    <n v="13"/>
+    <n v="13682.9"/>
+    <n v="1052.5307692307692"/>
+    <s v="Black"/>
+    <x v="9"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="FD13FCSBLA013"/>
+  </r>
+  <r>
+    <s v="GM09CMR014"/>
+    <s v="GM"/>
+    <s v="General Motors"/>
+    <s v="CMR"/>
+    <s v="Camero"/>
+    <s v="09"/>
+    <n v="17"/>
+    <n v="28464.799999999999"/>
+    <n v="1674.3999999999999"/>
+    <s v="White"/>
+    <x v="10"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="GM09CMRWHI014"/>
+  </r>
+  <r>
+    <s v="GM12CMR015"/>
+    <s v="GM"/>
+    <s v="General Motors"/>
+    <s v="CMR"/>
+    <s v="Camero"/>
+    <s v="12"/>
+    <n v="14"/>
+    <n v="19421.099999999999"/>
+    <n v="1387.2214285714285"/>
+    <s v="Black"/>
+    <x v="11"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="GM12CMRBLA015"/>
+  </r>
+  <r>
+    <s v="GM14CMR016"/>
+    <s v="GM"/>
+    <s v="General Motors"/>
+    <s v="CMR"/>
+    <s v="Camero"/>
+    <s v="14"/>
+    <n v="12"/>
+    <n v="14289.6"/>
+    <n v="1190.8"/>
+    <s v="White"/>
+    <x v="12"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="GM14CMRWHI016"/>
+  </r>
+  <r>
+    <s v="GM10SLV017"/>
+    <s v="GM"/>
+    <s v="General Motors"/>
+    <s v="SLV"/>
+    <s v="Silverado"/>
+    <s v="10"/>
+    <n v="16"/>
+    <n v="31144.400000000001"/>
+    <n v="1946.5250000000001"/>
+    <s v="Black"/>
+    <x v="13"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="GM10SLVBLA017"/>
+  </r>
+  <r>
+    <s v="GM98SLV018"/>
+    <s v="GM"/>
+    <s v="General Motors"/>
+    <s v="SLV"/>
+    <s v="Silverado"/>
+    <s v="98"/>
+    <n v="28"/>
+    <n v="83162.7"/>
+    <n v="2970.0964285714285"/>
+    <s v="Black"/>
+    <x v="10"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="GM98SLVBLA018"/>
+  </r>
+  <r>
+    <s v="GM00SLV019"/>
+    <s v="GM"/>
+    <s v="General Motors"/>
+    <s v="SLV"/>
+    <s v="Silverado"/>
+    <s v="00"/>
+    <n v="26"/>
+    <n v="80685.8"/>
+    <n v="3103.3"/>
+    <s v="Blue"/>
+    <x v="8"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="GM00SLVBLU019"/>
+  </r>
+  <r>
+    <s v="TY96CAM020"/>
+    <s v="TY"/>
+    <s v="Toyota"/>
+    <s v="CAM"/>
+    <s v="Camery"/>
+    <s v="96"/>
+    <n v="30"/>
+    <n v="114660.6"/>
+    <n v="3822.02"/>
+    <s v="Green"/>
+    <x v="14"/>
+    <n v="100000"/>
+    <s v="Not Covered"/>
+    <s v="TY96CAMGRE020"/>
+  </r>
+  <r>
+    <s v="TY98CAM021"/>
+    <s v="TY"/>
+    <s v="Toyota"/>
+    <s v="CAM"/>
+    <s v="Camery"/>
+    <s v="98"/>
+    <n v="28"/>
+    <n v="93382.6"/>
+    <n v="3335.0928571428572"/>
+    <s v="Black"/>
+    <x v="15"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="TY98CAMBLA021"/>
+  </r>
+  <r>
+    <s v="TY00CAM022"/>
+    <s v="TY"/>
+    <s v="Toyota"/>
+    <s v="CAM"/>
+    <s v="Camery"/>
+    <s v="00"/>
+    <n v="26"/>
+    <n v="85928"/>
+    <n v="3304.9230769230771"/>
+    <s v="Green"/>
+    <x v="4"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="TY00CAMGRE022"/>
+  </r>
+  <r>
+    <s v="TY02CAM023"/>
+    <s v="TY"/>
+    <s v="Toyota"/>
+    <s v="CAM"/>
+    <s v="Camery"/>
+    <s v="02"/>
+    <n v="24"/>
+    <n v="67829.100000000006"/>
+    <n v="2826.2125000000001"/>
+    <s v="Black"/>
+    <x v="0"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="TY02CAMBLA023"/>
+  </r>
+  <r>
+    <s v="TY09CAM024"/>
+    <s v="TY"/>
+    <s v="Toyota"/>
+    <s v="CAM"/>
+    <s v="Camery"/>
+    <s v="09"/>
+    <n v="17"/>
+    <n v="48114.2"/>
+    <n v="2830.2470588235292"/>
+    <s v="White"/>
+    <x v="5"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="TY09CAMWHI024"/>
+  </r>
+  <r>
+    <s v="TY02COR025"/>
+    <s v="TY"/>
+    <s v="Toyota"/>
+    <s v="COR"/>
+    <s v="Corola"/>
+    <s v="02"/>
+    <n v="24"/>
+    <n v="64467.4"/>
+    <n v="2686.1416666666669"/>
+    <s v="Red"/>
+    <x v="16"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="TY02CORRED025"/>
+  </r>
+  <r>
+    <s v="TY03COR026"/>
+    <s v="TY"/>
+    <s v="Toyota"/>
+    <s v="COR"/>
+    <s v="Corola"/>
+    <s v="03"/>
+    <n v="23"/>
+    <n v="73444.399999999994"/>
+    <n v="3193.2347826086952"/>
+    <s v="Black"/>
+    <x v="16"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="TY03CORBLA026"/>
+  </r>
+  <r>
+    <s v="TY14COR027"/>
+    <s v="TY"/>
+    <s v="Toyota"/>
+    <s v="COR"/>
+    <s v="Corola"/>
+    <s v="14"/>
+    <n v="12"/>
+    <n v="17556.3"/>
+    <n v="1463.0249999999999"/>
+    <s v="Blue"/>
+    <x v="6"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="TY14CORBLU027"/>
+  </r>
+  <r>
+    <s v="TY12COR028"/>
+    <s v="TY"/>
+    <s v="Toyota"/>
+    <s v="COR"/>
+    <s v="Corola"/>
+    <s v="12"/>
+    <n v="14"/>
+    <n v="29601.9"/>
+    <n v="2114.4214285714288"/>
+    <s v="Black"/>
+    <x v="10"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="TY12CORBLA028"/>
+  </r>
+  <r>
+    <s v="TY12CAM029"/>
+    <s v="TY"/>
+    <s v="Toyota"/>
+    <s v="CAM"/>
+    <s v="Camery"/>
+    <s v="12"/>
+    <n v="14"/>
+    <n v="22128.2"/>
+    <n v="1580.5857142857144"/>
+    <s v="Blue"/>
+    <x v="14"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="TY12CAMBLU029"/>
+  </r>
+  <r>
+    <s v="HO99CIV030"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="CIV"/>
+    <s v="Civic"/>
+    <s v="99"/>
+    <n v="27"/>
+    <n v="82374"/>
+    <n v="3050.8888888888887"/>
+    <s v="White"/>
+    <x v="9"/>
+    <n v="75000"/>
+    <s v="Not Covered"/>
+    <s v="HO99CIVWHI030"/>
+  </r>
+  <r>
+    <s v="HO01CIV031"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="CIV"/>
+    <s v="Civic"/>
+    <s v="01"/>
+    <n v="25"/>
+    <n v="69891.899999999994"/>
+    <n v="2795.6759999999999"/>
+    <s v="Blue"/>
+    <x v="3"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="HO01CIVBLU031"/>
+  </r>
+  <r>
+    <s v="HO10CIV032"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="CIV"/>
+    <s v="Civic"/>
+    <s v="10"/>
+    <n v="16"/>
+    <n v="22573"/>
+    <n v="1410.8125"/>
+    <s v="Blue"/>
+    <x v="12"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="HO10CIVBLU032"/>
+  </r>
+  <r>
+    <s v="HO10CIV033"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="CIV"/>
+    <s v="Civic"/>
+    <s v="10"/>
+    <n v="16"/>
+    <n v="33477.199999999997"/>
+    <n v="2092.3249999999998"/>
+    <s v="Black"/>
+    <x v="15"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="HO10CIVBLA033"/>
+  </r>
+  <r>
+    <s v="HO11CIV034"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="CIV"/>
+    <s v="Civic"/>
+    <s v="11"/>
+    <n v="15"/>
+    <n v="30555.3"/>
+    <n v="2037.02"/>
+    <s v="Black"/>
+    <x v="2"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="HO11CIVBLA034"/>
+  </r>
+  <r>
+    <s v="HO12CIV035"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="CIV"/>
+    <s v="Civic"/>
+    <s v="12"/>
+    <n v="14"/>
+    <n v="24513.200000000001"/>
+    <n v="1750.9428571428573"/>
+    <s v="Black"/>
+    <x v="13"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="HO12CIVBLA035"/>
+  </r>
+  <r>
+    <s v="HO13CIV036"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="CIV"/>
+    <s v="Civic"/>
+    <s v="13"/>
+    <n v="13"/>
+    <n v="13867.6"/>
+    <n v="1066.7384615384615"/>
+    <s v="Black"/>
+    <x v="14"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="HO13CIVBLA036"/>
+  </r>
+  <r>
+    <s v="HO05ODY037"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="ODY"/>
+    <s v="Odyssey"/>
+    <s v="05"/>
+    <n v="21"/>
+    <n v="60389.5"/>
+    <n v="2875.6904761904761"/>
+    <s v="White"/>
+    <x v="5"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="HO05ODYWHI037"/>
+  </r>
+  <r>
+    <s v="HO07ODY038"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="ODY"/>
+    <s v="Odyssey"/>
+    <s v="07"/>
+    <n v="19"/>
+    <n v="50854.1"/>
+    <n v="2676.5315789473684"/>
+    <s v="Black"/>
+    <x v="15"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="HO07ODYBLA038"/>
+  </r>
+  <r>
+    <s v="HO08ODY039"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="ODY"/>
+    <s v="Odyssey"/>
+    <s v="08"/>
+    <n v="18"/>
+    <n v="42504.6"/>
+    <n v="2361.3666666666668"/>
+    <s v="White"/>
+    <x v="9"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="HO08ODYWHI039"/>
+  </r>
+  <r>
+    <s v="HO01ODY040"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="ODY"/>
+    <s v="Odyssey"/>
+    <s v="01"/>
+    <n v="25"/>
+    <n v="68658.899999999994"/>
+    <n v="2746.3559999999998"/>
+    <s v="Black"/>
+    <x v="0"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="HO01ODYBLA040"/>
+  </r>
+  <r>
+    <s v="HO14ODY041"/>
+    <s v="HO"/>
+    <s v="Honda"/>
+    <s v="ODY"/>
+    <s v="Odyssey"/>
+    <s v="14"/>
+    <n v="12"/>
+    <n v="3708.1"/>
+    <n v="309.00833333333333"/>
+    <s v="Black"/>
+    <x v="1"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="HO14ODYBLA041"/>
+  </r>
+  <r>
+    <s v="CR04PTC042"/>
+    <s v="CR"/>
+    <s v="Chrysler"/>
+    <s v="PTC"/>
+    <s v="PT Cruiser"/>
+    <s v="04"/>
+    <n v="22"/>
+    <n v="64542"/>
+    <n v="2933.7272727272725"/>
+    <s v="Blue"/>
+    <x v="0"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="CR04PTCBLU042"/>
+  </r>
+  <r>
+    <s v="CR07PTC043"/>
+    <s v="CR"/>
+    <s v="Chrysler"/>
+    <s v="PTC"/>
+    <s v="PT Cruiser"/>
+    <s v="07"/>
+    <n v="19"/>
+    <n v="42074.2"/>
+    <n v="2214.4315789473681"/>
+    <s v="Green"/>
+    <x v="16"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="CR07PTCGRE043"/>
+  </r>
+  <r>
+    <s v="CR11PTC044"/>
+    <s v="CR"/>
+    <s v="Chrysler"/>
+    <s v="PTC"/>
+    <s v="PT Cruiser"/>
+    <s v="11"/>
+    <n v="15"/>
+    <n v="27394.2"/>
+    <n v="1826.28"/>
+    <s v="Black"/>
+    <x v="8"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="CR11PTCBLA044"/>
+  </r>
+  <r>
+    <s v="CR99CAR045"/>
+    <s v="CR"/>
+    <s v="Chrysler"/>
+    <s v="CAR"/>
+    <s v="Caravan"/>
+    <s v="99"/>
+    <n v="27"/>
+    <n v="79420.600000000006"/>
+    <n v="2941.5037037037041"/>
+    <s v="Green"/>
+    <x v="13"/>
+    <n v="75000"/>
+    <s v="Not Covered"/>
+    <s v="CR99CARGRE045"/>
+  </r>
+  <r>
+    <s v="CR00CAR046"/>
+    <s v="CR"/>
+    <s v="Chrysler"/>
+    <s v="CAR"/>
+    <s v="Caravan"/>
+    <s v="00"/>
+    <n v="26"/>
+    <n v="77243.100000000006"/>
+    <n v="2970.8884615384618"/>
+    <s v="Black"/>
+    <x v="3"/>
+    <n v="75000"/>
+    <s v="Not Covered"/>
+    <s v="CR00CARBLA046"/>
+  </r>
+  <r>
+    <s v="CR04CAR047"/>
+    <s v="CR"/>
+    <s v="Chrysler"/>
+    <s v="CAR"/>
+    <s v="Caravan"/>
+    <s v="04"/>
+    <n v="22"/>
+    <n v="72527.199999999997"/>
+    <n v="3296.6909090909089"/>
+    <s v="White"/>
+    <x v="11"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="CR04CARWHI047"/>
+  </r>
+  <r>
+    <s v="CR04CAR048"/>
+    <s v="CR"/>
+    <s v="Chrysler"/>
+    <s v="CAR"/>
+    <s v="Caravan"/>
+    <s v="04"/>
+    <n v="22"/>
+    <n v="52699.4"/>
+    <n v="2395.4272727272728"/>
+    <s v="Red"/>
+    <x v="11"/>
+    <n v="75000"/>
+    <s v="Y"/>
+    <s v="CR04CARRED048"/>
+  </r>
+  <r>
+    <s v="HY11ELA049"/>
+    <s v="HY"/>
+    <s v="Hyndai"/>
+    <s v="ELA"/>
+    <s v="Elantra"/>
+    <s v="11"/>
+    <n v="15"/>
+    <n v="29102.3"/>
+    <n v="1940.1533333333332"/>
+    <s v="Black"/>
+    <x v="12"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="HY11ELABLA049"/>
+  </r>
+  <r>
+    <s v="HY12ELA050"/>
+    <s v="HY"/>
+    <s v="Hyndai"/>
+    <s v="ELA"/>
+    <s v="Elantra"/>
+    <s v="12"/>
+    <n v="14"/>
+    <n v="22282"/>
+    <n v="1591.5714285714287"/>
+    <s v="Blue"/>
+    <x v="1"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="HY12ELABLU050"/>
+  </r>
+  <r>
+    <s v="HY13ELA051"/>
+    <s v="HY"/>
+    <s v="Hyndai"/>
+    <s v="ELA"/>
+    <s v="Elantra"/>
+    <s v="13"/>
+    <n v="13"/>
+    <n v="20223.900000000001"/>
+    <n v="1555.6846153846154"/>
+    <s v="Black"/>
+    <x v="6"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="HY13ELABLA051"/>
+  </r>
+  <r>
+    <s v="HY13ELA052"/>
+    <s v="HY"/>
+    <s v="Hyndai"/>
+    <s v="ELA"/>
+    <s v="Elantra"/>
+    <s v="13"/>
+    <n v="13"/>
+    <n v="22188.5"/>
+    <n v="1706.8076923076924"/>
+    <s v="Blue"/>
+    <x v="4"/>
+    <n v="100000"/>
+    <s v="Y"/>
+    <s v="HY13ELABLU052"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F9D07D03-D66E-42C9-A003-FE6413C8288E}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A3:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="18">
+        <item x="11"/>
+        <item x="14"/>
+        <item x="4"/>
+        <item x="16"/>
+        <item x="5"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="18">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Miles" fld="7" baseField="0" baseItem="0" numFmtId="43"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1309,6 +4920,173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A15015-9E9F-4B17-A3CA-FC0707E0A1DB}">
+  <dimension ref="A3:B21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="12">
+        <v>144647.69999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="12">
+        <v>150656.40000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="12">
+        <v>154427.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="12">
+        <v>179986</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="12">
+        <v>143640.70000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="12">
+        <v>135078.20000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="12">
+        <v>184693.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="12">
+        <v>127731.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="12">
+        <v>70964.899999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="12">
+        <v>65315</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="12">
+        <v>138561.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="12">
+        <v>141229.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="12">
+        <v>305432.40000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="12">
+        <v>177713.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="12">
+        <v>65964.899999999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="12">
+        <v>130601.59999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="12">
+        <v>19341.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="12">
+        <v>2335987.2999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1BE64A-6E35-46AF-B538-7FFA7D2A357E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1323,7 +5101,8 @@
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5546875" customWidth="1"/>
-    <col min="10" max="10" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" customWidth="1"/>
     <col min="12" max="12" width="9.6640625" customWidth="1"/>
     <col min="13" max="13" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.88671875" bestFit="1" customWidth="1"/>
@@ -1375,47 +5154,47 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B2" s="7" t="str">
         <f>LEFT(A2, 2)</f>
-        <v>FD</v>
+        <v>HO</v>
       </c>
       <c r="C2" s="5" t="str">
         <f>VLOOKUP(B2, $B$57:$C$62, 2)</f>
-        <v>Ford</v>
+        <v>Honda</v>
       </c>
       <c r="D2" s="7" t="str">
         <f>MID(A2, 5, 3)</f>
-        <v>MTG</v>
+        <v>ODY</v>
       </c>
       <c r="E2" s="4" t="str">
         <f>VLOOKUP(D2, D$57:E$67, 2)</f>
-        <v>Mustag</v>
+        <v>Odyssey</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>MID(A2, 3, 2)</f>
-        <v>06</v>
+        <v>14</v>
       </c>
       <c r="G2" s="4">
         <f>IF(26-F2&lt;0, 100-F2+26, 26-F2)</f>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H2" s="8">
-        <v>40326.800000000003</v>
+        <v>3708.1</v>
       </c>
       <c r="I2" s="8">
         <f>H2/G2</f>
-        <v>2016.3400000000001</v>
+        <v>309.00833333333333</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L2">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="M2" s="9" t="str">
         <f>IF(H2&lt;=L2, "Y", "Not Covered")</f>
@@ -1423,537 +5202,537 @@
       </c>
       <c r="N2" s="4" t="str">
         <f>CONCATENATE(B2,F2,D2,UPPER(LEFT(J2,3)),RIGHT(A2,3))</f>
-        <v>FD06MTGBLA001</v>
+        <v>HO14ODYBLA041</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B3" s="7" t="str">
-        <f t="shared" ref="B3:B53" si="0">LEFT(A3, 2)</f>
+        <f>LEFT(A3, 2)</f>
         <v>FD</v>
       </c>
       <c r="C3" s="5" t="str">
-        <f t="shared" ref="C3:C53" si="1">VLOOKUP(B3, $B$57:$C$62, 2)</f>
+        <f>VLOOKUP(B3, $B$57:$C$62, 2)</f>
         <v>Ford</v>
       </c>
       <c r="D3" s="7" t="str">
-        <f t="shared" ref="D3:D53" si="2">MID(A3, 5, 3)</f>
-        <v>MTG</v>
+        <f>MID(A3, 5, 3)</f>
+        <v>FCS</v>
       </c>
       <c r="E3" s="4" t="str">
-        <f t="shared" ref="E3:E53" si="3">VLOOKUP(D3, D$57:E$67, 2)</f>
-        <v>Mustag</v>
+        <f>VLOOKUP(D3, D$57:E$67, 2)</f>
+        <v>Focus</v>
       </c>
       <c r="F3" s="4" t="str">
-        <f t="shared" ref="F3:F53" si="4">MID(A3, 3, 2)</f>
-        <v>06</v>
+        <f>MID(A3, 3, 2)</f>
+        <v>13</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" ref="G3:G53" si="5">IF(26-F3&lt;0, 100-F3+26, 26-F3)</f>
-        <v>20</v>
+        <f>IF(26-F3&lt;0, 100-F3+26, 26-F3)</f>
+        <v>13</v>
       </c>
       <c r="H3" s="8">
-        <v>44974.8</v>
+        <v>13682.9</v>
       </c>
       <c r="I3" s="8">
-        <f t="shared" ref="I3:I53" si="6">H3/G3</f>
-        <v>2248.7400000000002</v>
+        <f>H3/G3</f>
+        <v>1052.5307692307692</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="L3">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="M3" s="9" t="str">
-        <f t="shared" ref="M3:M53" si="7">IF(H3&lt;=L3, "Y", "Not Covered")</f>
+        <f>IF(H3&lt;=L3, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N3" s="4" t="str">
-        <f t="shared" ref="N3:N53" si="8">CONCATENATE(B3,F3,D3,UPPER(LEFT(J3,3)),RIGHT(A3,3))</f>
-        <v>FD06MTGWHI002</v>
+        <f>CONCATENATE(B3,F3,D3,UPPER(LEFT(J3,3)),RIGHT(A3,3))</f>
+        <v>FD13FCSBLA013</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="B4" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>FD</v>
+        <f>LEFT(A4, 2)</f>
+        <v>HO</v>
       </c>
       <c r="C4" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Ford</v>
+        <f>VLOOKUP(B4, $B$57:$C$62, 2)</f>
+        <v>Honda</v>
       </c>
       <c r="D4" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>MTG</v>
+        <f>MID(A4, 5, 3)</f>
+        <v>CIV</v>
       </c>
       <c r="E4" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Mustag</v>
+        <f>VLOOKUP(D4, D$57:E$67, 2)</f>
+        <v>Civic</v>
       </c>
       <c r="F4" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>08</v>
+        <f>MID(A4, 3, 2)</f>
+        <v>13</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="5"/>
-        <v>18</v>
+        <f>IF(26-F4&lt;0, 100-F4+26, 26-F4)</f>
+        <v>13</v>
       </c>
       <c r="H4" s="8">
-        <v>44946.5</v>
+        <v>13867.6</v>
       </c>
       <c r="I4" s="8">
-        <f t="shared" si="6"/>
-        <v>2497.0277777777778</v>
+        <f>H4/G4</f>
+        <v>1066.7384615384615</v>
       </c>
       <c r="J4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="L4">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="M4" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H4&lt;=L4, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N4" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>FD08MTGGRE003</v>
+        <f>CONCATENATE(B4,F4,D4,UPPER(LEFT(J4,3)),RIGHT(A4,3))</f>
+        <v>HO13CIVBLA036</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B5" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>FD</v>
+        <f>LEFT(A5, 2)</f>
+        <v>GM</v>
       </c>
       <c r="C5" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Ford</v>
+        <f>VLOOKUP(B5, $B$57:$C$62, 2)</f>
+        <v>General Motors</v>
       </c>
       <c r="D5" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>MTG</v>
+        <f>MID(A5, 5, 3)</f>
+        <v>CMR</v>
       </c>
       <c r="E5" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Mustag</v>
+        <f>VLOOKUP(D5, D$57:E$67, 2)</f>
+        <v>Camero</v>
       </c>
       <c r="F5" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>08</v>
+        <f>MID(A5, 3, 2)</f>
+        <v>14</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="5"/>
+        <f>IF(26-F5&lt;0, 100-F5+26, 26-F5)</f>
+        <v>12</v>
+      </c>
+      <c r="H5" s="8">
+        <v>14289.6</v>
+      </c>
+      <c r="I5" s="8">
+        <f>H5/G5</f>
+        <v>1190.8</v>
+      </c>
+      <c r="J5" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="8">
-        <v>37558.800000000003</v>
-      </c>
-      <c r="I5" s="8">
-        <f t="shared" si="6"/>
-        <v>2086.6000000000004</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
       <c r="K5" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L5">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="M5" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H5&lt;=L5, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N5" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>FD08MTGBLA004</v>
+        <f>CONCATENATE(B5,F5,D5,UPPER(LEFT(J5,3)),RIGHT(A5,3))</f>
+        <v>GM14CMRWHI016</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B6" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>FD</v>
+        <f>LEFT(A6, 2)</f>
+        <v>TY</v>
       </c>
       <c r="C6" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Ford</v>
+        <f>VLOOKUP(B6, $B$57:$C$62, 2)</f>
+        <v>Toyota</v>
       </c>
       <c r="D6" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>MTG</v>
+        <f>MID(A6, 5, 3)</f>
+        <v>COR</v>
       </c>
       <c r="E6" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Mustag</v>
+        <f>VLOOKUP(D6, D$57:E$67, 2)</f>
+        <v>Corola</v>
       </c>
       <c r="F6" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>08</v>
+        <f>MID(A6, 3, 2)</f>
+        <v>14</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="5"/>
-        <v>18</v>
+        <f>IF(26-F6&lt;0, 100-F6+26, 26-F6)</f>
+        <v>12</v>
       </c>
       <c r="H6" s="8">
-        <v>36438.5</v>
+        <v>17556.3</v>
       </c>
       <c r="I6" s="8">
-        <f t="shared" si="6"/>
-        <v>2024.3611111111111</v>
+        <f>H6/G6</f>
+        <v>1463.0249999999999</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="L6">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="M6" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H6&lt;=L6, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N6" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>FD08MTGWHI005</v>
+        <f>CONCATENATE(B6,F6,D6,UPPER(LEFT(J6,3)),RIGHT(A6,3))</f>
+        <v>TY14CORBLU027</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="B7" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A7, 2)</f>
         <v>FD</v>
       </c>
       <c r="C7" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B7, $B$57:$C$62, 2)</f>
         <v>Ford</v>
       </c>
       <c r="D7" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>MID(A7, 5, 3)</f>
         <v>FCS</v>
       </c>
       <c r="E7" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f>VLOOKUP(D7, D$57:E$67, 2)</f>
         <v>Focus</v>
       </c>
       <c r="F7" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>06</v>
+        <f>MID(A7, 3, 2)</f>
+        <v>12</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f>IF(26-F7&lt;0, 100-F7+26, 26-F7)</f>
+        <v>14</v>
       </c>
       <c r="H7" s="8">
-        <v>46311.4</v>
+        <v>19341.7</v>
       </c>
       <c r="I7" s="8">
-        <f t="shared" si="6"/>
-        <v>2315.5700000000002</v>
+        <f>H7/G7</f>
+        <v>1381.55</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L7">
         <v>75000</v>
       </c>
       <c r="M7" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H7&lt;=L7, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N7" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>FD06FCSGRE006</v>
+        <f>CONCATENATE(B7,F7,D7,UPPER(LEFT(J7,3)),RIGHT(A7,3))</f>
+        <v>FD12FCSWHI011</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B8" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>FD</v>
+        <f>LEFT(A8, 2)</f>
+        <v>GM</v>
       </c>
       <c r="C8" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Ford</v>
+        <f>VLOOKUP(B8, $B$57:$C$62, 2)</f>
+        <v>General Motors</v>
       </c>
       <c r="D8" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>FCS</v>
+        <f>MID(A8, 5, 3)</f>
+        <v>CMR</v>
       </c>
       <c r="E8" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Focus</v>
+        <f>VLOOKUP(D8, D$57:E$67, 2)</f>
+        <v>Camero</v>
       </c>
       <c r="F8" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>06</v>
+        <f>MID(A8, 3, 2)</f>
+        <v>12</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f>IF(26-F8&lt;0, 100-F8+26, 26-F8)</f>
+        <v>14</v>
       </c>
       <c r="H8" s="8">
-        <v>52229.5</v>
+        <v>19421.099999999999</v>
       </c>
       <c r="I8" s="8">
-        <f t="shared" si="6"/>
-        <v>2611.4749999999999</v>
+        <f>H8/G8</f>
+        <v>1387.2214285714285</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="L8">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="M8" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H8&lt;=L8, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N8" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>FD06FCSGRE007</v>
+        <f>CONCATENATE(B8,F8,D8,UPPER(LEFT(J8,3)),RIGHT(A8,3))</f>
+        <v>GM12CMRBLA015</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="B9" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>FD</v>
+        <f>LEFT(A9, 2)</f>
+        <v>HY</v>
       </c>
       <c r="C9" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Ford</v>
+        <f>VLOOKUP(B9, $B$57:$C$62, 2)</f>
+        <v>Hyndai</v>
       </c>
       <c r="D9" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>FCS</v>
+        <f>MID(A9, 5, 3)</f>
+        <v>ELA</v>
       </c>
       <c r="E9" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Focus</v>
+        <f>VLOOKUP(D9, D$57:E$67, 2)</f>
+        <v>Elantra</v>
       </c>
       <c r="F9" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>09</v>
+        <f>MID(A9, 3, 2)</f>
+        <v>13</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="5"/>
-        <v>17</v>
+        <f>IF(26-F9&lt;0, 100-F9+26, 26-F9)</f>
+        <v>13</v>
       </c>
       <c r="H9" s="8">
-        <v>35137</v>
+        <v>20223.900000000001</v>
       </c>
       <c r="I9" s="8">
-        <f t="shared" si="6"/>
-        <v>2066.8823529411766</v>
+        <f>H9/G9</f>
+        <v>1555.6846153846154</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L9">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="M9" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H9&lt;=L9, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N9" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>FD09FCSBLA008</v>
+        <f>CONCATENATE(B9,F9,D9,UPPER(LEFT(J9,3)),RIGHT(A9,3))</f>
+        <v>HY13ELABLA051</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="B10" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>FD</v>
+        <f>LEFT(A10, 2)</f>
+        <v>TY</v>
       </c>
       <c r="C10" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Ford</v>
+        <f>VLOOKUP(B10, $B$57:$C$62, 2)</f>
+        <v>Toyota</v>
       </c>
       <c r="D10" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>FCS</v>
+        <f>MID(A10, 5, 3)</f>
+        <v>CAM</v>
       </c>
       <c r="E10" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Focus</v>
+        <f>VLOOKUP(D10, D$57:E$67, 2)</f>
+        <v>Camery</v>
       </c>
       <c r="F10" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>13</v>
+        <f>MID(A10, 3, 2)</f>
+        <v>12</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="5"/>
-        <v>13</v>
+        <f>IF(26-F10&lt;0, 100-F10+26, 26-F10)</f>
+        <v>14</v>
       </c>
       <c r="H10" s="8">
-        <v>27637.1</v>
+        <v>22128.2</v>
       </c>
       <c r="I10" s="8">
-        <f t="shared" si="6"/>
-        <v>2125.9307692307693</v>
+        <f>H10/G10</f>
+        <v>1580.5857142857144</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="L10">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="M10" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H10&lt;=L10, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N10" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>FD13FCSBLA009</v>
+        <f>CONCATENATE(B10,F10,D10,UPPER(LEFT(J10,3)),RIGHT(A10,3))</f>
+        <v>TY12CAMBLU029</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="B11" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>FD</v>
+        <f>LEFT(A11, 2)</f>
+        <v>HY</v>
       </c>
       <c r="C11" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Ford</v>
+        <f>VLOOKUP(B11, $B$57:$C$62, 2)</f>
+        <v>Hyndai</v>
       </c>
       <c r="D11" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>FCS</v>
+        <f>MID(A11, 5, 3)</f>
+        <v>ELA</v>
       </c>
       <c r="E11" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Focus</v>
+        <f>VLOOKUP(D11, D$57:E$67, 2)</f>
+        <v>Elantra</v>
       </c>
       <c r="F11" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f>MID(A11, 3, 2)</f>
         <v>13</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="5"/>
+        <f>IF(26-F11&lt;0, 100-F11+26, 26-F11)</f>
         <v>13</v>
       </c>
       <c r="H11" s="8">
-        <v>27534.799999999999</v>
+        <v>22188.5</v>
       </c>
       <c r="I11" s="8">
-        <f t="shared" si="6"/>
-        <v>2118.0615384615385</v>
+        <f>H11/G11</f>
+        <v>1706.8076923076924</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K11" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L11">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="M11" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H11&lt;=L11, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N11" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>FD13FCSWHI010</v>
+        <f>CONCATENATE(B11,F11,D11,UPPER(LEFT(J11,3)),RIGHT(A11,3))</f>
+        <v>HY13ELABLU052</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="B12" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>FD</v>
+        <f>LEFT(A12, 2)</f>
+        <v>HY</v>
       </c>
       <c r="C12" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Ford</v>
+        <f>VLOOKUP(B12, $B$57:$C$62, 2)</f>
+        <v>Hyndai</v>
       </c>
       <c r="D12" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>FCS</v>
+        <f>MID(A12, 5, 3)</f>
+        <v>ELA</v>
       </c>
       <c r="E12" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Focus</v>
+        <f>VLOOKUP(D12, D$57:E$67, 2)</f>
+        <v>Elantra</v>
       </c>
       <c r="F12" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f>MID(A12, 3, 2)</f>
         <v>12</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="5"/>
+        <f>IF(26-F12&lt;0, 100-F12+26, 26-F12)</f>
         <v>14</v>
       </c>
       <c r="H12" s="8">
-        <v>19341.7</v>
+        <v>22282</v>
       </c>
       <c r="I12" s="8">
-        <f t="shared" si="6"/>
-        <v>1381.55</v>
+        <f>H12/G12</f>
+        <v>1591.5714285714287</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K12" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="L12">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="M12" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H12&lt;=L12, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N12" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>FD12FCSWHI011</v>
+        <f>CONCATENATE(B12,F12,D12,UPPER(LEFT(J12,3)),RIGHT(A12,3))</f>
+        <v>HY12ELABLU050</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1961,34 +5740,34 @@
         <v>35</v>
       </c>
       <c r="B13" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A13, 2)</f>
         <v>FD</v>
       </c>
       <c r="C13" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B13, $B$57:$C$62, 2)</f>
         <v>Ford</v>
       </c>
       <c r="D13" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>MID(A13, 5, 3)</f>
         <v>FCS</v>
       </c>
       <c r="E13" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f>VLOOKUP(D13, D$57:E$67, 2)</f>
         <v>Focus</v>
       </c>
       <c r="F13" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f>MID(A13, 3, 2)</f>
         <v>13</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="5"/>
+        <f>IF(26-F13&lt;0, 100-F13+26, 26-F13)</f>
         <v>13</v>
       </c>
       <c r="H13" s="8">
         <v>22521.599999999999</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" si="6"/>
+        <f>H13/G13</f>
         <v>1732.4307692307691</v>
       </c>
       <c r="J13" t="s">
@@ -2001,316 +5780,316 @@
         <v>75000</v>
       </c>
       <c r="M13" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H13&lt;=L13, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N13" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f>CONCATENATE(B13,F13,D13,UPPER(LEFT(J13,3)),RIGHT(A13,3))</f>
         <v>FD13FCSBLA012</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="B14" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>FD</v>
+        <f>LEFT(A14, 2)</f>
+        <v>HO</v>
       </c>
       <c r="C14" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Ford</v>
+        <f>VLOOKUP(B14, $B$57:$C$62, 2)</f>
+        <v>Honda</v>
       </c>
       <c r="D14" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>FCS</v>
+        <f>MID(A14, 5, 3)</f>
+        <v>CIV</v>
       </c>
       <c r="E14" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Focus</v>
+        <f>VLOOKUP(D14, D$57:E$67, 2)</f>
+        <v>Civic</v>
       </c>
       <c r="F14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>13</v>
+        <f>MID(A14, 3, 2)</f>
+        <v>10</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="5"/>
-        <v>13</v>
+        <f>IF(26-F14&lt;0, 100-F14+26, 26-F14)</f>
+        <v>16</v>
       </c>
       <c r="H14" s="8">
-        <v>13682.9</v>
+        <v>22573</v>
       </c>
       <c r="I14" s="8">
-        <f t="shared" si="6"/>
-        <v>1052.5307692307692</v>
+        <f>H14/G14</f>
+        <v>1410.8125</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="K14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L14">
         <v>75000</v>
       </c>
       <c r="M14" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H14&lt;=L14, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N14" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>FD13FCSBLA013</v>
+        <f>CONCATENATE(B14,F14,D14,UPPER(LEFT(J14,3)),RIGHT(A14,3))</f>
+        <v>HO10CIVBLU032</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="B15" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>GM</v>
+        <f>LEFT(A15, 2)</f>
+        <v>HO</v>
       </c>
       <c r="C15" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>General Motors</v>
+        <f>VLOOKUP(B15, $B$57:$C$62, 2)</f>
+        <v>Honda</v>
       </c>
       <c r="D15" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CMR</v>
+        <f>MID(A15, 5, 3)</f>
+        <v>CIV</v>
       </c>
       <c r="E15" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Camero</v>
+        <f>VLOOKUP(D15, D$57:E$67, 2)</f>
+        <v>Civic</v>
       </c>
       <c r="F15" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>09</v>
+        <f>MID(A15, 3, 2)</f>
+        <v>12</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="5"/>
-        <v>17</v>
+        <f>IF(26-F15&lt;0, 100-F15+26, 26-F15)</f>
+        <v>14</v>
       </c>
       <c r="H15" s="8">
-        <v>28464.799999999999</v>
+        <v>24513.200000000001</v>
       </c>
       <c r="I15" s="8">
-        <f t="shared" si="6"/>
-        <v>1674.3999999999999</v>
+        <f>H15/G15</f>
+        <v>1750.9428571428573</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L15">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="M15" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H15&lt;=L15, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N15" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>GM09CMRWHI014</v>
+        <f>CONCATENATE(B15,F15,D15,UPPER(LEFT(J15,3)),RIGHT(A15,3))</f>
+        <v>HO12CIVBLA035</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="B16" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>GM</v>
+        <f>LEFT(A16, 2)</f>
+        <v>CR</v>
       </c>
       <c r="C16" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>General Motors</v>
+        <f>VLOOKUP(B16, $B$57:$C$62, 2)</f>
+        <v>Chrysler</v>
       </c>
       <c r="D16" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CMR</v>
+        <f>MID(A16, 5, 3)</f>
+        <v>PTC</v>
       </c>
       <c r="E16" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Camero</v>
+        <f>VLOOKUP(D16, D$57:E$67, 2)</f>
+        <v>PT Cruiser</v>
       </c>
       <c r="F16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>12</v>
+        <f>MID(A16, 3, 2)</f>
+        <v>11</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="5"/>
-        <v>14</v>
+        <f>IF(26-F16&lt;0, 100-F16+26, 26-F16)</f>
+        <v>15</v>
       </c>
       <c r="H16" s="8">
-        <v>19421.099999999999</v>
+        <v>27394.2</v>
       </c>
       <c r="I16" s="8">
-        <f t="shared" si="6"/>
-        <v>1387.2214285714285</v>
+        <f>H16/G16</f>
+        <v>1826.28</v>
       </c>
       <c r="J16" t="s">
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L16">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="M16" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H16&lt;=L16, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N16" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>GM12CMRBLA015</v>
+        <f>CONCATENATE(B16,F16,D16,UPPER(LEFT(J16,3)),RIGHT(A16,3))</f>
+        <v>CR11PTCBLA044</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B17" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>GM</v>
+        <f>LEFT(A17, 2)</f>
+        <v>FD</v>
       </c>
       <c r="C17" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>General Motors</v>
+        <f>VLOOKUP(B17, $B$57:$C$62, 2)</f>
+        <v>Ford</v>
       </c>
       <c r="D17" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CMR</v>
+        <f>MID(A17, 5, 3)</f>
+        <v>FCS</v>
       </c>
       <c r="E17" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Camero</v>
+        <f>VLOOKUP(D17, D$57:E$67, 2)</f>
+        <v>Focus</v>
       </c>
       <c r="F17" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>14</v>
+        <f>MID(A17, 3, 2)</f>
+        <v>13</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
+        <f>IF(26-F17&lt;0, 100-F17+26, 26-F17)</f>
+        <v>13</v>
       </c>
       <c r="H17" s="8">
-        <v>14289.6</v>
+        <v>27534.799999999999</v>
       </c>
       <c r="I17" s="8">
-        <f t="shared" si="6"/>
-        <v>1190.8</v>
+        <f>H17/G17</f>
+        <v>2118.0615384615385</v>
       </c>
       <c r="J17" t="s">
         <v>18</v>
       </c>
       <c r="K17" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L17">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="M17" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H17&lt;=L17, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N17" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>GM14CMRWHI016</v>
+        <f>CONCATENATE(B17,F17,D17,UPPER(LEFT(J17,3)),RIGHT(A17,3))</f>
+        <v>FD13FCSWHI010</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B18" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>GM</v>
+        <f>LEFT(A18, 2)</f>
+        <v>FD</v>
       </c>
       <c r="C18" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>General Motors</v>
+        <f>VLOOKUP(B18, $B$57:$C$62, 2)</f>
+        <v>Ford</v>
       </c>
       <c r="D18" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>SLV</v>
+        <f>MID(A18, 5, 3)</f>
+        <v>FCS</v>
       </c>
       <c r="E18" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Silverado</v>
+        <f>VLOOKUP(D18, D$57:E$67, 2)</f>
+        <v>Focus</v>
       </c>
       <c r="F18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>10</v>
+        <f>MID(A18, 3, 2)</f>
+        <v>13</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="5"/>
-        <v>16</v>
+        <f>IF(26-F18&lt;0, 100-F18+26, 26-F18)</f>
+        <v>13</v>
       </c>
       <c r="H18" s="8">
-        <v>31144.400000000001</v>
+        <v>27637.1</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="6"/>
-        <v>1946.5250000000001</v>
+        <f>H18/G18</f>
+        <v>2125.9307692307693</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="L18">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="M18" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H18&lt;=L18, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N18" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>GM10SLVBLA017</v>
+        <f>CONCATENATE(B18,F18,D18,UPPER(LEFT(J18,3)),RIGHT(A18,3))</f>
+        <v>FD13FCSBLA009</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="B19" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A19, 2)</f>
         <v>GM</v>
       </c>
       <c r="C19" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B19, $B$57:$C$62, 2)</f>
         <v>General Motors</v>
       </c>
       <c r="D19" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>SLV</v>
+        <f>MID(A19, 5, 3)</f>
+        <v>CMR</v>
       </c>
       <c r="E19" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Silverado</v>
+        <f>VLOOKUP(D19, D$57:E$67, 2)</f>
+        <v>Camero</v>
       </c>
       <c r="F19" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>98</v>
+        <f>MID(A19, 3, 2)</f>
+        <v>09</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="5"/>
-        <v>28</v>
+        <f>IF(26-F19&lt;0, 100-F19+26, 26-F19)</f>
+        <v>17</v>
       </c>
       <c r="H19" s="8">
-        <v>83162.7</v>
+        <v>28464.799999999999</v>
       </c>
       <c r="I19" s="8">
-        <f t="shared" si="6"/>
-        <v>2970.0964285714285</v>
+        <f>H19/G19</f>
+        <v>1674.3999999999999</v>
       </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
@@ -2319,966 +6098,966 @@
         <v>100000</v>
       </c>
       <c r="M19" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H19&lt;=L19, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N19" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>GM98SLVBLA018</v>
+        <f>CONCATENATE(B19,F19,D19,UPPER(LEFT(J19,3)),RIGHT(A19,3))</f>
+        <v>GM09CMRWHI014</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="B20" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>GM</v>
+        <f>LEFT(A20, 2)</f>
+        <v>HY</v>
       </c>
       <c r="C20" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>General Motors</v>
+        <f>VLOOKUP(B20, $B$57:$C$62, 2)</f>
+        <v>Hyndai</v>
       </c>
       <c r="D20" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>SLV</v>
+        <f>MID(A20, 5, 3)</f>
+        <v>ELA</v>
       </c>
       <c r="E20" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Silverado</v>
+        <f>VLOOKUP(D20, D$57:E$67, 2)</f>
+        <v>Elantra</v>
       </c>
       <c r="F20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>00</v>
+        <f>MID(A20, 3, 2)</f>
+        <v>11</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="5"/>
-        <v>26</v>
+        <f>IF(26-F20&lt;0, 100-F20+26, 26-F20)</f>
+        <v>15</v>
       </c>
       <c r="H20" s="8">
-        <v>80685.8</v>
+        <v>29102.3</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="6"/>
-        <v>3103.3</v>
+        <f>H20/G20</f>
+        <v>1940.1533333333332</v>
       </c>
       <c r="J20" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L20">
         <v>100000</v>
       </c>
       <c r="M20" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H20&lt;=L20, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N20" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>GM00SLVBLU019</v>
+        <f>CONCATENATE(B20,F20,D20,UPPER(LEFT(J20,3)),RIGHT(A20,3))</f>
+        <v>HY11ELABLA049</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B21" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A21, 2)</f>
         <v>TY</v>
       </c>
       <c r="C21" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B21, $B$57:$C$62, 2)</f>
         <v>Toyota</v>
       </c>
       <c r="D21" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CAM</v>
+        <f>MID(A21, 5, 3)</f>
+        <v>COR</v>
       </c>
       <c r="E21" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Camery</v>
+        <f>VLOOKUP(D21, D$57:E$67, 2)</f>
+        <v>Corola</v>
       </c>
       <c r="F21" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>96</v>
+        <f>MID(A21, 3, 2)</f>
+        <v>12</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="5"/>
-        <v>30</v>
+        <f>IF(26-F21&lt;0, 100-F21+26, 26-F21)</f>
+        <v>14</v>
       </c>
       <c r="H21" s="8">
-        <v>114660.6</v>
+        <v>29601.9</v>
       </c>
       <c r="I21" s="8">
-        <f t="shared" si="6"/>
-        <v>3822.02</v>
+        <f>H21/G21</f>
+        <v>2114.4214285714288</v>
       </c>
       <c r="J21" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="L21">
         <v>100000</v>
       </c>
       <c r="M21" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>Not Covered</v>
+        <f>IF(H21&lt;=L21, "Y", "Not Covered")</f>
+        <v>Y</v>
       </c>
       <c r="N21" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>TY96CAMGRE020</v>
+        <f>CONCATENATE(B21,F21,D21,UPPER(LEFT(J21,3)),RIGHT(A21,3))</f>
+        <v>TY12CORBLA028</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B22" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>TY</v>
+        <f>LEFT(A22, 2)</f>
+        <v>HO</v>
       </c>
       <c r="C22" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Toyota</v>
+        <f>VLOOKUP(B22, $B$57:$C$62, 2)</f>
+        <v>Honda</v>
       </c>
       <c r="D22" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CAM</v>
+        <f>MID(A22, 5, 3)</f>
+        <v>CIV</v>
       </c>
       <c r="E22" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Camery</v>
+        <f>VLOOKUP(D22, D$57:E$67, 2)</f>
+        <v>Civic</v>
       </c>
       <c r="F22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>98</v>
+        <f>MID(A22, 3, 2)</f>
+        <v>11</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="5"/>
-        <v>28</v>
+        <f>IF(26-F22&lt;0, 100-F22+26, 26-F22)</f>
+        <v>15</v>
       </c>
       <c r="H22" s="8">
-        <v>93382.6</v>
+        <v>30555.3</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" si="6"/>
-        <v>3335.0928571428572</v>
+        <f>H22/G22</f>
+        <v>2037.02</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="L22">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="M22" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H22&lt;=L22, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N22" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>TY98CAMBLA021</v>
+        <f>CONCATENATE(B22,F22,D22,UPPER(LEFT(J22,3)),RIGHT(A22,3))</f>
+        <v>HO11CIVBLA034</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B23" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>TY</v>
+        <f>LEFT(A23, 2)</f>
+        <v>GM</v>
       </c>
       <c r="C23" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Toyota</v>
+        <f>VLOOKUP(B23, $B$57:$C$62, 2)</f>
+        <v>General Motors</v>
       </c>
       <c r="D23" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CAM</v>
+        <f>MID(A23, 5, 3)</f>
+        <v>SLV</v>
       </c>
       <c r="E23" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Camery</v>
+        <f>VLOOKUP(D23, D$57:E$67, 2)</f>
+        <v>Silverado</v>
       </c>
       <c r="F23" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>00</v>
+        <f>MID(A23, 3, 2)</f>
+        <v>10</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="5"/>
-        <v>26</v>
+        <f>IF(26-F23&lt;0, 100-F23+26, 26-F23)</f>
+        <v>16</v>
       </c>
       <c r="H23" s="8">
-        <v>85928</v>
+        <v>31144.400000000001</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="6"/>
-        <v>3304.9230769230771</v>
+        <f>H23/G23</f>
+        <v>1946.5250000000001</v>
       </c>
       <c r="J23" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L23">
         <v>100000</v>
       </c>
       <c r="M23" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H23&lt;=L23, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N23" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>TY00CAMGRE022</v>
+        <f>CONCATENATE(B23,F23,D23,UPPER(LEFT(J23,3)),RIGHT(A23,3))</f>
+        <v>GM10SLVBLA017</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B24" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>TY</v>
+        <f>LEFT(A24, 2)</f>
+        <v>HO</v>
       </c>
       <c r="C24" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Toyota</v>
+        <f>VLOOKUP(B24, $B$57:$C$62, 2)</f>
+        <v>Honda</v>
       </c>
       <c r="D24" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CAM</v>
+        <f>MID(A24, 5, 3)</f>
+        <v>CIV</v>
       </c>
       <c r="E24" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Camery</v>
+        <f>VLOOKUP(D24, D$57:E$67, 2)</f>
+        <v>Civic</v>
       </c>
       <c r="F24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>02</v>
+        <f>MID(A24, 3, 2)</f>
+        <v>10</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="5"/>
-        <v>24</v>
+        <f>IF(26-F24&lt;0, 100-F24+26, 26-F24)</f>
+        <v>16</v>
       </c>
       <c r="H24" s="8">
-        <v>67829.100000000006</v>
+        <v>33477.199999999997</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="6"/>
-        <v>2826.2125000000001</v>
+        <f>H24/G24</f>
+        <v>2092.3249999999998</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="L24">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="M24" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H24&lt;=L24, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N24" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>TY02CAMBLA023</v>
+        <f>CONCATENATE(B24,F24,D24,UPPER(LEFT(J24,3)),RIGHT(A24,3))</f>
+        <v>HO10CIVBLA033</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B25" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>TY</v>
+        <f>LEFT(A25, 2)</f>
+        <v>FD</v>
       </c>
       <c r="C25" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Toyota</v>
+        <f>VLOOKUP(B25, $B$57:$C$62, 2)</f>
+        <v>Ford</v>
       </c>
       <c r="D25" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CAM</v>
+        <f>MID(A25, 5, 3)</f>
+        <v>FCS</v>
       </c>
       <c r="E25" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Camery</v>
+        <f>VLOOKUP(D25, D$57:E$67, 2)</f>
+        <v>Focus</v>
       </c>
       <c r="F25" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f>MID(A25, 3, 2)</f>
         <v>09</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="5"/>
+        <f>IF(26-F25&lt;0, 100-F25+26, 26-F25)</f>
         <v>17</v>
       </c>
       <c r="H25" s="8">
-        <v>48114.2</v>
+        <v>35137</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="6"/>
-        <v>2830.2470588235292</v>
+        <f>H25/G25</f>
+        <v>2066.8823529411766</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K25" t="s">
         <v>29</v>
       </c>
       <c r="L25">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="M25" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H25&lt;=L25, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N25" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>TY09CAMWHI024</v>
+        <f>CONCATENATE(B25,F25,D25,UPPER(LEFT(J25,3)),RIGHT(A25,3))</f>
+        <v>FD09FCSBLA008</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="B26" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>TY</v>
+        <f>LEFT(A26, 2)</f>
+        <v>FD</v>
       </c>
       <c r="C26" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Toyota</v>
+        <f>VLOOKUP(B26, $B$57:$C$62, 2)</f>
+        <v>Ford</v>
       </c>
       <c r="D26" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>COR</v>
+        <f>MID(A26, 5, 3)</f>
+        <v>MTG</v>
       </c>
       <c r="E26" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Corola</v>
+        <f>VLOOKUP(D26, D$57:E$67, 2)</f>
+        <v>Mustag</v>
       </c>
       <c r="F26" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>02</v>
+        <f>MID(A26, 3, 2)</f>
+        <v>08</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="5"/>
-        <v>24</v>
+        <f>IF(26-F26&lt;0, 100-F26+26, 26-F26)</f>
+        <v>18</v>
       </c>
       <c r="H26" s="8">
-        <v>64467.4</v>
+        <v>36438.5</v>
       </c>
       <c r="I26" s="8">
-        <f t="shared" si="6"/>
-        <v>2686.1416666666669</v>
+        <f>H26/G26</f>
+        <v>2024.3611111111111</v>
       </c>
       <c r="J26" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="K26" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="L26">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="M26" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H26&lt;=L26, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N26" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>TY02CORRED025</v>
+        <f>CONCATENATE(B26,F26,D26,UPPER(LEFT(J26,3)),RIGHT(A26,3))</f>
+        <v>FD08MTGWHI005</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="B27" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>TY</v>
+        <f>LEFT(A27, 2)</f>
+        <v>FD</v>
       </c>
       <c r="C27" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Toyota</v>
+        <f>VLOOKUP(B27, $B$57:$C$62, 2)</f>
+        <v>Ford</v>
       </c>
       <c r="D27" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>COR</v>
+        <f>MID(A27, 5, 3)</f>
+        <v>MTG</v>
       </c>
       <c r="E27" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Corola</v>
+        <f>VLOOKUP(D27, D$57:E$67, 2)</f>
+        <v>Mustag</v>
       </c>
       <c r="F27" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>03</v>
+        <f>MID(A27, 3, 2)</f>
+        <v>08</v>
       </c>
       <c r="G27" s="4">
-        <f t="shared" si="5"/>
-        <v>23</v>
+        <f>IF(26-F27&lt;0, 100-F27+26, 26-F27)</f>
+        <v>18</v>
       </c>
       <c r="H27" s="8">
-        <v>73444.399999999994</v>
+        <v>37558.800000000003</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" si="6"/>
-        <v>3193.2347826086952</v>
+        <f>H27/G27</f>
+        <v>2086.6000000000004</v>
       </c>
       <c r="J27" t="s">
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="L27">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="M27" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H27&lt;=L27, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N27" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>TY03CORBLA026</v>
+        <f>CONCATENATE(B27,F27,D27,UPPER(LEFT(J27,3)),RIGHT(A27,3))</f>
+        <v>FD08MTGBLA004</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="B28" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>TY</v>
+        <f>LEFT(A28, 2)</f>
+        <v>FD</v>
       </c>
       <c r="C28" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Toyota</v>
+        <f>VLOOKUP(B28, $B$57:$C$62, 2)</f>
+        <v>Ford</v>
       </c>
       <c r="D28" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>COR</v>
+        <f>MID(A28, 5, 3)</f>
+        <v>MTG</v>
       </c>
       <c r="E28" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Corola</v>
+        <f>VLOOKUP(D28, D$57:E$67, 2)</f>
+        <v>Mustag</v>
       </c>
       <c r="F28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>14</v>
+        <f>MID(A28, 3, 2)</f>
+        <v>06</v>
       </c>
       <c r="G28" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
+        <f>IF(26-F28&lt;0, 100-F28+26, 26-F28)</f>
+        <v>20</v>
       </c>
       <c r="H28" s="8">
-        <v>17556.3</v>
+        <v>40326.800000000003</v>
       </c>
       <c r="I28" s="8">
-        <f t="shared" si="6"/>
-        <v>1463.0249999999999</v>
+        <f>H28/G28</f>
+        <v>2016.3400000000001</v>
       </c>
       <c r="J28" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="L28">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="M28" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H28&lt;=L28, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N28" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>TY14CORBLU027</v>
+        <f>CONCATENATE(B28,F28,D28,UPPER(LEFT(J28,3)),RIGHT(A28,3))</f>
+        <v>FD06MTGBLA001</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B29" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>TY</v>
+        <f>LEFT(A29, 2)</f>
+        <v>CR</v>
       </c>
       <c r="C29" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Toyota</v>
+        <f>VLOOKUP(B29, $B$57:$C$62, 2)</f>
+        <v>Chrysler</v>
       </c>
       <c r="D29" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>COR</v>
+        <f>MID(A29, 5, 3)</f>
+        <v>PTC</v>
       </c>
       <c r="E29" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Corola</v>
+        <f>VLOOKUP(D29, D$57:E$67, 2)</f>
+        <v>PT Cruiser</v>
       </c>
       <c r="F29" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>12</v>
+        <f>MID(A29, 3, 2)</f>
+        <v>07</v>
       </c>
       <c r="G29" s="4">
-        <f t="shared" si="5"/>
-        <v>14</v>
+        <f>IF(26-F29&lt;0, 100-F29+26, 26-F29)</f>
+        <v>19</v>
       </c>
       <c r="H29" s="8">
-        <v>29601.9</v>
+        <v>42074.2</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" si="6"/>
-        <v>2114.4214285714288</v>
+        <f>H29/G29</f>
+        <v>2214.4315789473681</v>
       </c>
       <c r="J29" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="L29">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="M29" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H29&lt;=L29, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N29" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>TY12CORBLA028</v>
+        <f>CONCATENATE(B29,F29,D29,UPPER(LEFT(J29,3)),RIGHT(A29,3))</f>
+        <v>CR07PTCGRE043</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B30" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>TY</v>
+        <f>LEFT(A30, 2)</f>
+        <v>HO</v>
       </c>
       <c r="C30" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Toyota</v>
+        <f>VLOOKUP(B30, $B$57:$C$62, 2)</f>
+        <v>Honda</v>
       </c>
       <c r="D30" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CAM</v>
+        <f>MID(A30, 5, 3)</f>
+        <v>ODY</v>
       </c>
       <c r="E30" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Camery</v>
+        <f>VLOOKUP(D30, D$57:E$67, 2)</f>
+        <v>Odyssey</v>
       </c>
       <c r="F30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>12</v>
+        <f>MID(A30, 3, 2)</f>
+        <v>08</v>
       </c>
       <c r="G30" s="4">
-        <f t="shared" si="5"/>
-        <v>14</v>
+        <f>IF(26-F30&lt;0, 100-F30+26, 26-F30)</f>
+        <v>18</v>
       </c>
       <c r="H30" s="8">
-        <v>22128.2</v>
+        <v>42504.6</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" si="6"/>
-        <v>1580.5857142857144</v>
+        <f>H30/G30</f>
+        <v>2361.3666666666668</v>
       </c>
       <c r="J30" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L30">
         <v>100000</v>
       </c>
       <c r="M30" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H30&lt;=L30, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N30" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>TY12CAMBLU029</v>
+        <f>CONCATENATE(B30,F30,D30,UPPER(LEFT(J30,3)),RIGHT(A30,3))</f>
+        <v>HO08ODYWHI039</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="B31" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HO</v>
+        <f>LEFT(A31, 2)</f>
+        <v>FD</v>
       </c>
       <c r="C31" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Honda</v>
+        <f>VLOOKUP(B31, $B$57:$C$62, 2)</f>
+        <v>Ford</v>
       </c>
       <c r="D31" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CIV</v>
+        <f>MID(A31, 5, 3)</f>
+        <v>MTG</v>
       </c>
       <c r="E31" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Civic</v>
+        <f>VLOOKUP(D31, D$57:E$67, 2)</f>
+        <v>Mustag</v>
       </c>
       <c r="F31" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>99</v>
+        <f>MID(A31, 3, 2)</f>
+        <v>08</v>
       </c>
       <c r="G31" s="4">
-        <f t="shared" si="5"/>
-        <v>27</v>
+        <f>IF(26-F31&lt;0, 100-F31+26, 26-F31)</f>
+        <v>18</v>
       </c>
       <c r="H31" s="8">
-        <v>82374</v>
+        <v>44946.5</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" si="6"/>
-        <v>3050.8888888888887</v>
+        <f>H31/G31</f>
+        <v>2497.0277777777778</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="L31">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="M31" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>Not Covered</v>
+        <f>IF(H31&lt;=L31, "Y", "Not Covered")</f>
+        <v>Y</v>
       </c>
       <c r="N31" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO99CIVWHI030</v>
+        <f>CONCATENATE(B31,F31,D31,UPPER(LEFT(J31,3)),RIGHT(A31,3))</f>
+        <v>FD08MTGGRE003</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="B32" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HO</v>
+        <f>LEFT(A32, 2)</f>
+        <v>FD</v>
       </c>
       <c r="C32" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Honda</v>
+        <f>VLOOKUP(B32, $B$57:$C$62, 2)</f>
+        <v>Ford</v>
       </c>
       <c r="D32" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CIV</v>
+        <f>MID(A32, 5, 3)</f>
+        <v>MTG</v>
       </c>
       <c r="E32" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Civic</v>
+        <f>VLOOKUP(D32, D$57:E$67, 2)</f>
+        <v>Mustag</v>
       </c>
       <c r="F32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>01</v>
+        <f>MID(A32, 3, 2)</f>
+        <v>06</v>
       </c>
       <c r="G32" s="4">
-        <f t="shared" si="5"/>
-        <v>25</v>
+        <f>IF(26-F32&lt;0, 100-F32+26, 26-F32)</f>
+        <v>20</v>
       </c>
       <c r="H32" s="8">
-        <v>69891.899999999994</v>
+        <v>44974.8</v>
       </c>
       <c r="I32" s="8">
-        <f t="shared" si="6"/>
-        <v>2795.6759999999999</v>
+        <f>H32/G32</f>
+        <v>2248.7400000000002</v>
       </c>
       <c r="J32" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="K32" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L32">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="M32" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H32&lt;=L32, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N32" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO01CIVBLU031</v>
+        <f>CONCATENATE(B32,F32,D32,UPPER(LEFT(J32,3)),RIGHT(A32,3))</f>
+        <v>FD06MTGWHI002</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="B33" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HO</v>
+        <f>LEFT(A33, 2)</f>
+        <v>FD</v>
       </c>
       <c r="C33" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Honda</v>
+        <f>VLOOKUP(B33, $B$57:$C$62, 2)</f>
+        <v>Ford</v>
       </c>
       <c r="D33" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CIV</v>
+        <f>MID(A33, 5, 3)</f>
+        <v>FCS</v>
       </c>
       <c r="E33" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Civic</v>
+        <f>VLOOKUP(D33, D$57:E$67, 2)</f>
+        <v>Focus</v>
       </c>
       <c r="F33" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>10</v>
+        <f>MID(A33, 3, 2)</f>
+        <v>06</v>
       </c>
       <c r="G33" s="4">
-        <f t="shared" si="5"/>
-        <v>16</v>
+        <f>IF(26-F33&lt;0, 100-F33+26, 26-F33)</f>
+        <v>20</v>
       </c>
       <c r="H33" s="8">
-        <v>22573</v>
+        <v>46311.4</v>
       </c>
       <c r="I33" s="8">
-        <f t="shared" si="6"/>
-        <v>1410.8125</v>
+        <f>H33/G33</f>
+        <v>2315.5700000000002</v>
       </c>
       <c r="J33" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="L33">
         <v>75000</v>
       </c>
       <c r="M33" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H33&lt;=L33, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N33" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO10CIVBLU032</v>
+        <f>CONCATENATE(B33,F33,D33,UPPER(LEFT(J33,3)),RIGHT(A33,3))</f>
+        <v>FD06FCSGRE006</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B34" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HO</v>
+        <f>LEFT(A34, 2)</f>
+        <v>TY</v>
       </c>
       <c r="C34" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Honda</v>
+        <f>VLOOKUP(B34, $B$57:$C$62, 2)</f>
+        <v>Toyota</v>
       </c>
       <c r="D34" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CIV</v>
+        <f>MID(A34, 5, 3)</f>
+        <v>CAM</v>
       </c>
       <c r="E34" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Civic</v>
+        <f>VLOOKUP(D34, D$57:E$67, 2)</f>
+        <v>Camery</v>
       </c>
       <c r="F34" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>10</v>
+        <f>MID(A34, 3, 2)</f>
+        <v>09</v>
       </c>
       <c r="G34" s="4">
-        <f t="shared" si="5"/>
-        <v>16</v>
+        <f>IF(26-F34&lt;0, 100-F34+26, 26-F34)</f>
+        <v>17</v>
       </c>
       <c r="H34" s="8">
-        <v>33477.199999999997</v>
+        <v>48114.2</v>
       </c>
       <c r="I34" s="8">
-        <f t="shared" si="6"/>
-        <v>2092.3249999999998</v>
+        <f>H34/G34</f>
+        <v>2830.2470588235292</v>
       </c>
       <c r="J34" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K34" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="L34">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="M34" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H34&lt;=L34, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N34" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO10CIVBLA033</v>
+        <f>CONCATENATE(B34,F34,D34,UPPER(LEFT(J34,3)),RIGHT(A34,3))</f>
+        <v>TY09CAMWHI024</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B35" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A35, 2)</f>
         <v>HO</v>
       </c>
       <c r="C35" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B35, $B$57:$C$62, 2)</f>
         <v>Honda</v>
       </c>
       <c r="D35" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CIV</v>
+        <f>MID(A35, 5, 3)</f>
+        <v>ODY</v>
       </c>
       <c r="E35" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Civic</v>
+        <f>VLOOKUP(D35, D$57:E$67, 2)</f>
+        <v>Odyssey</v>
       </c>
       <c r="F35" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f>MID(A35, 3, 2)</f>
+        <v>07</v>
       </c>
       <c r="G35" s="4">
-        <f t="shared" si="5"/>
-        <v>15</v>
+        <f>IF(26-F35&lt;0, 100-F35+26, 26-F35)</f>
+        <v>19</v>
       </c>
       <c r="H35" s="8">
-        <v>30555.3</v>
+        <v>50854.1</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" si="6"/>
-        <v>2037.02</v>
+        <f>H35/G35</f>
+        <v>2676.5315789473684</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="L35">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="M35" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H35&lt;=L35, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N35" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO11CIVBLA034</v>
+        <f>CONCATENATE(B35,F35,D35,UPPER(LEFT(J35,3)),RIGHT(A35,3))</f>
+        <v>HO07ODYBLA038</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="B36" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HO</v>
+        <f>LEFT(A36, 2)</f>
+        <v>FD</v>
       </c>
       <c r="C36" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Honda</v>
+        <f>VLOOKUP(B36, $B$57:$C$62, 2)</f>
+        <v>Ford</v>
       </c>
       <c r="D36" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CIV</v>
+        <f>MID(A36, 5, 3)</f>
+        <v>FCS</v>
       </c>
       <c r="E36" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Civic</v>
+        <f>VLOOKUP(D36, D$57:E$67, 2)</f>
+        <v>Focus</v>
       </c>
       <c r="F36" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>12</v>
+        <f>MID(A36, 3, 2)</f>
+        <v>06</v>
       </c>
       <c r="G36" s="4">
-        <f t="shared" si="5"/>
-        <v>14</v>
+        <f>IF(26-F36&lt;0, 100-F36+26, 26-F36)</f>
+        <v>20</v>
       </c>
       <c r="H36" s="8">
-        <v>24513.200000000001</v>
+        <v>52229.5</v>
       </c>
       <c r="I36" s="8">
-        <f t="shared" si="6"/>
-        <v>1750.9428571428573</v>
+        <f>H36/G36</f>
+        <v>2611.4749999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="L36">
         <v>75000</v>
       </c>
       <c r="M36" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H36&lt;=L36, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N36" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO12CIVBLA035</v>
+        <f>CONCATENATE(B36,F36,D36,UPPER(LEFT(J36,3)),RIGHT(A36,3))</f>
+        <v>FD06FCSGRE007</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B37" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HO</v>
+        <f>LEFT(A37, 2)</f>
+        <v>CR</v>
       </c>
       <c r="C37" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Honda</v>
+        <f>VLOOKUP(B37, $B$57:$C$62, 2)</f>
+        <v>Chrysler</v>
       </c>
       <c r="D37" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CIV</v>
+        <f>MID(A37, 5, 3)</f>
+        <v>CAR</v>
       </c>
       <c r="E37" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Civic</v>
+        <f>VLOOKUP(D37, D$57:E$67, 2)</f>
+        <v>Caravan</v>
       </c>
       <c r="F37" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>13</v>
+        <f>MID(A37, 3, 2)</f>
+        <v>04</v>
       </c>
       <c r="G37" s="4">
-        <f t="shared" si="5"/>
-        <v>13</v>
+        <f>IF(26-F37&lt;0, 100-F37+26, 26-F37)</f>
+        <v>22</v>
       </c>
       <c r="H37" s="8">
-        <v>13867.6</v>
+        <v>52699.4</v>
       </c>
       <c r="I37" s="8">
-        <f t="shared" si="6"/>
-        <v>1066.7384615384615</v>
+        <f>H37/G37</f>
+        <v>2395.4272727272728</v>
       </c>
       <c r="J37" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="K37" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="L37">
         <v>75000</v>
       </c>
       <c r="M37" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H37&lt;=L37, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N37" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO13CIVBLA036</v>
+        <f>CONCATENATE(B37,F37,D37,UPPER(LEFT(J37,3)),RIGHT(A37,3))</f>
+        <v>CR04CARRED048</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -3286,34 +7065,34 @@
         <v>121</v>
       </c>
       <c r="B38" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A38, 2)</f>
         <v>HO</v>
       </c>
       <c r="C38" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B38, $B$57:$C$62, 2)</f>
         <v>Honda</v>
       </c>
       <c r="D38" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>MID(A38, 5, 3)</f>
         <v>ODY</v>
       </c>
       <c r="E38" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f>VLOOKUP(D38, D$57:E$67, 2)</f>
         <v>Odyssey</v>
       </c>
       <c r="F38" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f>MID(A38, 3, 2)</f>
         <v>05</v>
       </c>
       <c r="G38" s="4">
-        <f t="shared" si="5"/>
+        <f>IF(26-F38&lt;0, 100-F38+26, 26-F38)</f>
         <v>21</v>
       </c>
       <c r="H38" s="8">
         <v>60389.5</v>
       </c>
       <c r="I38" s="8">
-        <f t="shared" si="6"/>
+        <f>H38/G38</f>
         <v>2875.6904761904761</v>
       </c>
       <c r="J38" t="s">
@@ -3326,154 +7105,154 @@
         <v>100000</v>
       </c>
       <c r="M38" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H38&lt;=L38, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N38" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f>CONCATENATE(B38,F38,D38,UPPER(LEFT(J38,3)),RIGHT(A38,3))</f>
         <v>HO05ODYWHI037</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B39" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HO</v>
+        <f>LEFT(A39, 2)</f>
+        <v>TY</v>
       </c>
       <c r="C39" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Honda</v>
+        <f>VLOOKUP(B39, $B$57:$C$62, 2)</f>
+        <v>Toyota</v>
       </c>
       <c r="D39" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>ODY</v>
+        <f>MID(A39, 5, 3)</f>
+        <v>COR</v>
       </c>
       <c r="E39" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Odyssey</v>
+        <f>VLOOKUP(D39, D$57:E$67, 2)</f>
+        <v>Corola</v>
       </c>
       <c r="F39" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>07</v>
+        <f>MID(A39, 3, 2)</f>
+        <v>02</v>
       </c>
       <c r="G39" s="4">
-        <f t="shared" si="5"/>
-        <v>19</v>
+        <f>IF(26-F39&lt;0, 100-F39+26, 26-F39)</f>
+        <v>24</v>
       </c>
       <c r="H39" s="8">
-        <v>50854.1</v>
+        <v>64467.4</v>
       </c>
       <c r="I39" s="8">
-        <f t="shared" si="6"/>
-        <v>2676.5315789473684</v>
+        <f>H39/G39</f>
+        <v>2686.1416666666669</v>
       </c>
       <c r="J39" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="K39" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L39">
         <v>100000</v>
       </c>
       <c r="M39" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H39&lt;=L39, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N39" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO07ODYBLA038</v>
+        <f>CONCATENATE(B39,F39,D39,UPPER(LEFT(J39,3)),RIGHT(A39,3))</f>
+        <v>TY02CORRED025</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B40" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HO</v>
+        <f>LEFT(A40, 2)</f>
+        <v>CR</v>
       </c>
       <c r="C40" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Honda</v>
+        <f>VLOOKUP(B40, $B$57:$C$62, 2)</f>
+        <v>Chrysler</v>
       </c>
       <c r="D40" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>ODY</v>
+        <f>MID(A40, 5, 3)</f>
+        <v>PTC</v>
       </c>
       <c r="E40" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Odyssey</v>
+        <f>VLOOKUP(D40, D$57:E$67, 2)</f>
+        <v>PT Cruiser</v>
       </c>
       <c r="F40" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>08</v>
+        <f>MID(A40, 3, 2)</f>
+        <v>04</v>
       </c>
       <c r="G40" s="4">
-        <f t="shared" si="5"/>
-        <v>18</v>
+        <f>IF(26-F40&lt;0, 100-F40+26, 26-F40)</f>
+        <v>22</v>
       </c>
       <c r="H40" s="8">
-        <v>42504.6</v>
+        <v>64542</v>
       </c>
       <c r="I40" s="8">
-        <f t="shared" si="6"/>
-        <v>2361.3666666666668</v>
+        <f>H40/G40</f>
+        <v>2933.7272727272725</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K40" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="L40">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="M40" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H40&lt;=L40, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N40" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO08ODYWHI039</v>
+        <f>CONCATENATE(B40,F40,D40,UPPER(LEFT(J40,3)),RIGHT(A40,3))</f>
+        <v>CR04PTCBLU042</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="B41" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HO</v>
+        <f>LEFT(A41, 2)</f>
+        <v>TY</v>
       </c>
       <c r="C41" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Honda</v>
+        <f>VLOOKUP(B41, $B$57:$C$62, 2)</f>
+        <v>Toyota</v>
       </c>
       <c r="D41" s="7" t="str">
         <f>MID(A41, 5, 3)</f>
-        <v>ODY</v>
+        <v>CAM</v>
       </c>
       <c r="E41" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Odyssey</v>
+        <f>VLOOKUP(D41, D$57:E$67, 2)</f>
+        <v>Camery</v>
       </c>
       <c r="F41" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>01</v>
+        <f>MID(A41, 3, 2)</f>
+        <v>02</v>
       </c>
       <c r="G41" s="4">
-        <f t="shared" si="5"/>
-        <v>25</v>
+        <f>IF(26-F41&lt;0, 100-F41+26, 26-F41)</f>
+        <v>24</v>
       </c>
       <c r="H41" s="8">
-        <v>68658.899999999994</v>
+        <v>67829.100000000006</v>
       </c>
       <c r="I41" s="8">
-        <f t="shared" si="6"/>
-        <v>2746.3559999999998</v>
+        <f>H41/G41</f>
+        <v>2826.2125000000001</v>
       </c>
       <c r="J41" t="s">
         <v>15</v>
@@ -3485,648 +7264,648 @@
         <v>100000</v>
       </c>
       <c r="M41" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H41&lt;=L41, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N41" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO01ODYBLA040</v>
+        <f>CONCATENATE(B41,F41,D41,UPPER(LEFT(J41,3)),RIGHT(A41,3))</f>
+        <v>TY02CAMBLA023</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="B42" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A42, 2)</f>
         <v>HO</v>
       </c>
       <c r="C42" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B42, $B$57:$C$62, 2)</f>
         <v>Honda</v>
       </c>
       <c r="D42" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>MID(A42, 5, 3)</f>
         <v>ODY</v>
       </c>
       <c r="E42" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f>VLOOKUP(D42, D$57:E$67, 2)</f>
         <v>Odyssey</v>
       </c>
       <c r="F42" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>14</v>
+        <f>MID(A42, 3, 2)</f>
+        <v>01</v>
       </c>
       <c r="G42" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
+        <f>IF(26-F42&lt;0, 100-F42+26, 26-F42)</f>
+        <v>25</v>
       </c>
       <c r="H42" s="8">
-        <v>3708.1</v>
+        <v>68658.899999999994</v>
       </c>
       <c r="I42" s="8">
-        <f t="shared" si="6"/>
-        <v>309.00833333333333</v>
+        <f>H42/G42</f>
+        <v>2746.3559999999998</v>
       </c>
       <c r="J42" t="s">
         <v>15</v>
       </c>
       <c r="K42" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L42">
         <v>100000</v>
       </c>
       <c r="M42" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H42&lt;=L42, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N42" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HO14ODYBLA041</v>
+        <f>CONCATENATE(B42,F42,D42,UPPER(LEFT(J42,3)),RIGHT(A42,3))</f>
+        <v>HO01ODYBLA040</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B43" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>CR</v>
+        <f>LEFT(A43, 2)</f>
+        <v>HO</v>
       </c>
       <c r="C43" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Chrysler</v>
+        <f>VLOOKUP(B43, $B$57:$C$62, 2)</f>
+        <v>Honda</v>
       </c>
       <c r="D43" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>PTC</v>
+        <f>MID(A43, 5, 3)</f>
+        <v>CIV</v>
       </c>
       <c r="E43" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>PT Cruiser</v>
+        <f>VLOOKUP(D43, D$57:E$67, 2)</f>
+        <v>Civic</v>
       </c>
       <c r="F43" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>04</v>
+        <f>MID(A43, 3, 2)</f>
+        <v>01</v>
       </c>
       <c r="G43" s="4">
-        <f t="shared" si="5"/>
-        <v>22</v>
+        <f>IF(26-F43&lt;0, 100-F43+26, 26-F43)</f>
+        <v>25</v>
       </c>
       <c r="H43" s="8">
-        <v>64542</v>
+        <v>69891.899999999994</v>
       </c>
       <c r="I43" s="8">
-        <f t="shared" si="6"/>
-        <v>2933.7272727272725</v>
+        <f>H43/G43</f>
+        <v>2795.6759999999999</v>
       </c>
       <c r="J43" t="s">
         <v>48</v>
       </c>
       <c r="K43" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L43">
         <v>75000</v>
       </c>
       <c r="M43" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H43&lt;=L43, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N43" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>CR04PTCBLU042</v>
+        <f>CONCATENATE(B43,F43,D43,UPPER(LEFT(J43,3)),RIGHT(A43,3))</f>
+        <v>HO01CIVBLU031</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B44" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A44, 2)</f>
         <v>CR</v>
       </c>
       <c r="C44" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B44, $B$57:$C$62, 2)</f>
         <v>Chrysler</v>
       </c>
       <c r="D44" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>PTC</v>
+        <f>MID(A44, 5, 3)</f>
+        <v>CAR</v>
       </c>
       <c r="E44" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>PT Cruiser</v>
+        <f>VLOOKUP(D44, D$57:E$67, 2)</f>
+        <v>Caravan</v>
       </c>
       <c r="F44" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>07</v>
+        <f>MID(A44, 3, 2)</f>
+        <v>04</v>
       </c>
       <c r="G44" s="4">
-        <f t="shared" si="5"/>
-        <v>19</v>
+        <f>IF(26-F44&lt;0, 100-F44+26, 26-F44)</f>
+        <v>22</v>
       </c>
       <c r="H44" s="8">
-        <v>42074.2</v>
+        <v>72527.199999999997</v>
       </c>
       <c r="I44" s="8">
-        <f t="shared" si="6"/>
-        <v>2214.4315789473681</v>
+        <f>H44/G44</f>
+        <v>3296.6909090909089</v>
       </c>
       <c r="J44" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K44" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L44">
         <v>75000</v>
       </c>
       <c r="M44" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H44&lt;=L44, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N44" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>CR07PTCGRE043</v>
+        <f>CONCATENATE(B44,F44,D44,UPPER(LEFT(J44,3)),RIGHT(A44,3))</f>
+        <v>CR04CARWHI047</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="B45" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>CR</v>
+        <f>LEFT(A45, 2)</f>
+        <v>TY</v>
       </c>
       <c r="C45" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Chrysler</v>
+        <f>VLOOKUP(B45, $B$57:$C$62, 2)</f>
+        <v>Toyota</v>
       </c>
       <c r="D45" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>PTC</v>
+        <f>MID(A45, 5, 3)</f>
+        <v>COR</v>
       </c>
       <c r="E45" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>PT Cruiser</v>
+        <f>VLOOKUP(D45, D$57:E$67, 2)</f>
+        <v>Corola</v>
       </c>
       <c r="F45" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f>MID(A45, 3, 2)</f>
+        <v>03</v>
       </c>
       <c r="G45" s="4">
-        <f t="shared" si="5"/>
-        <v>15</v>
+        <f>IF(26-F45&lt;0, 100-F45+26, 26-F45)</f>
+        <v>23</v>
       </c>
       <c r="H45" s="8">
-        <v>27394.2</v>
+        <v>73444.399999999994</v>
       </c>
       <c r="I45" s="8">
-        <f t="shared" si="6"/>
-        <v>1826.28</v>
+        <f>H45/G45</f>
+        <v>3193.2347826086952</v>
       </c>
       <c r="J45" t="s">
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="L45">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="M45" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H45&lt;=L45, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N45" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>CR11PTCBLA044</v>
+        <f>CONCATENATE(B45,F45,D45,UPPER(LEFT(J45,3)),RIGHT(A45,3))</f>
+        <v>TY03CORBLA026</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B46" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A46, 2)</f>
         <v>CR</v>
       </c>
       <c r="C46" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B46, $B$57:$C$62, 2)</f>
         <v>Chrysler</v>
       </c>
       <c r="D46" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>MID(A46, 5, 3)</f>
         <v>CAR</v>
       </c>
       <c r="E46" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f>VLOOKUP(D46, D$57:E$67, 2)</f>
         <v>Caravan</v>
       </c>
       <c r="F46" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>99</v>
+        <f>MID(A46, 3, 2)</f>
+        <v>00</v>
       </c>
       <c r="G46" s="4">
-        <f t="shared" si="5"/>
-        <v>27</v>
+        <f>IF(26-F46&lt;0, 100-F46+26, 26-F46)</f>
+        <v>26</v>
       </c>
       <c r="H46" s="8">
-        <v>79420.600000000006</v>
+        <v>77243.100000000006</v>
       </c>
       <c r="I46" s="8">
-        <f t="shared" si="6"/>
-        <v>2941.5037037037041</v>
+        <f>H46/G46</f>
+        <v>2970.8884615384618</v>
       </c>
       <c r="J46" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="L46">
         <v>75000</v>
       </c>
       <c r="M46" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H46&lt;=L46, "Y", "Not Covered")</f>
         <v>Not Covered</v>
       </c>
       <c r="N46" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>CR99CARGRE045</v>
+        <f>CONCATENATE(B46,F46,D46,UPPER(LEFT(J46,3)),RIGHT(A46,3))</f>
+        <v>CR00CARBLA046</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B47" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A47, 2)</f>
         <v>CR</v>
       </c>
       <c r="C47" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B47, $B$57:$C$62, 2)</f>
         <v>Chrysler</v>
       </c>
       <c r="D47" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>MID(A47, 5, 3)</f>
         <v>CAR</v>
       </c>
       <c r="E47" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f>VLOOKUP(D47, D$57:E$67, 2)</f>
         <v>Caravan</v>
       </c>
       <c r="F47" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>00</v>
+        <f>MID(A47, 3, 2)</f>
+        <v>99</v>
       </c>
       <c r="G47" s="4">
-        <f t="shared" si="5"/>
-        <v>26</v>
+        <f>IF(26-F47&lt;0, 100-F47+26, 26-F47)</f>
+        <v>27</v>
       </c>
       <c r="H47" s="8">
-        <v>77243.100000000006</v>
+        <v>79420.600000000006</v>
       </c>
       <c r="I47" s="8">
-        <f t="shared" si="6"/>
-        <v>2970.8884615384618</v>
+        <f>H47/G47</f>
+        <v>2941.5037037037041</v>
       </c>
       <c r="J47" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L47">
         <v>75000</v>
       </c>
       <c r="M47" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H47&lt;=L47, "Y", "Not Covered")</f>
         <v>Not Covered</v>
       </c>
       <c r="N47" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>CR00CARBLA046</v>
+        <f>CONCATENATE(B47,F47,D47,UPPER(LEFT(J47,3)),RIGHT(A47,3))</f>
+        <v>CR99CARGRE045</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="B48" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>CR</v>
+        <f>LEFT(A48, 2)</f>
+        <v>GM</v>
       </c>
       <c r="C48" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Chrysler</v>
+        <f>VLOOKUP(B48, $B$57:$C$62, 2)</f>
+        <v>General Motors</v>
       </c>
       <c r="D48" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CAR</v>
+        <f>MID(A48, 5, 3)</f>
+        <v>SLV</v>
       </c>
       <c r="E48" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Caravan</v>
+        <f>VLOOKUP(D48, D$57:E$67, 2)</f>
+        <v>Silverado</v>
       </c>
       <c r="F48" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>04</v>
+        <f>MID(A48, 3, 2)</f>
+        <v>00</v>
       </c>
       <c r="G48" s="4">
-        <f t="shared" si="5"/>
-        <v>22</v>
+        <f>IF(26-F48&lt;0, 100-F48+26, 26-F48)</f>
+        <v>26</v>
       </c>
       <c r="H48" s="8">
-        <v>72527.199999999997</v>
+        <v>80685.8</v>
       </c>
       <c r="I48" s="8">
-        <f t="shared" si="6"/>
-        <v>3296.6909090909089</v>
+        <f>H48/G48</f>
+        <v>3103.3</v>
       </c>
       <c r="J48" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K48" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L48">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="M48" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H48&lt;=L48, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N48" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>CR04CARWHI047</v>
+        <f>CONCATENATE(B48,F48,D48,UPPER(LEFT(J48,3)),RIGHT(A48,3))</f>
+        <v>GM00SLVBLU019</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B49" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>CR</v>
+        <f>LEFT(A49, 2)</f>
+        <v>HO</v>
       </c>
       <c r="C49" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Chrysler</v>
+        <f>VLOOKUP(B49, $B$57:$C$62, 2)</f>
+        <v>Honda</v>
       </c>
       <c r="D49" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>CAR</v>
+        <f>MID(A49, 5, 3)</f>
+        <v>CIV</v>
       </c>
       <c r="E49" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Caravan</v>
+        <f>VLOOKUP(D49, D$57:E$67, 2)</f>
+        <v>Civic</v>
       </c>
       <c r="F49" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>04</v>
+        <f>MID(A49, 3, 2)</f>
+        <v>99</v>
       </c>
       <c r="G49" s="4">
-        <f t="shared" si="5"/>
-        <v>22</v>
+        <f>IF(26-F49&lt;0, 100-F49+26, 26-F49)</f>
+        <v>27</v>
       </c>
       <c r="H49" s="8">
-        <v>52699.4</v>
+        <v>82374</v>
       </c>
       <c r="I49" s="8">
-        <f t="shared" si="6"/>
-        <v>2395.4272727272728</v>
+        <f>H49/G49</f>
+        <v>3050.8888888888887</v>
       </c>
       <c r="J49" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L49">
         <v>75000</v>
       </c>
       <c r="M49" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>Y</v>
+        <f>IF(H49&lt;=L49, "Y", "Not Covered")</f>
+        <v>Not Covered</v>
       </c>
       <c r="N49" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>CR04CARRED048</v>
+        <f>CONCATENATE(B49,F49,D49,UPPER(LEFT(J49,3)),RIGHT(A49,3))</f>
+        <v>HO99CIVWHI030</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="B50" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HY</v>
+        <f>LEFT(A50, 2)</f>
+        <v>GM</v>
       </c>
       <c r="C50" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Hyndai</v>
+        <f>VLOOKUP(B50, $B$57:$C$62, 2)</f>
+        <v>General Motors</v>
       </c>
       <c r="D50" s="7" t="str">
         <f>MID(A50, 5, 3)</f>
-        <v>ELA</v>
+        <v>SLV</v>
       </c>
       <c r="E50" s="4" t="str">
         <f>VLOOKUP(D50, D$57:E$67, 2)</f>
-        <v>Elantra</v>
+        <v>Silverado</v>
       </c>
       <c r="F50" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f>MID(A50, 3, 2)</f>
+        <v>98</v>
       </c>
       <c r="G50" s="4">
-        <f t="shared" si="5"/>
-        <v>15</v>
+        <f>IF(26-F50&lt;0, 100-F50+26, 26-F50)</f>
+        <v>28</v>
       </c>
       <c r="H50" s="8">
-        <v>29102.3</v>
+        <v>83162.7</v>
       </c>
       <c r="I50" s="8">
-        <f t="shared" si="6"/>
-        <v>1940.1533333333332</v>
+        <f>H50/G50</f>
+        <v>2970.0964285714285</v>
       </c>
       <c r="J50" t="s">
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L50">
         <v>100000</v>
       </c>
       <c r="M50" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H50&lt;=L50, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N50" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HY11ELABLA049</v>
+        <f>CONCATENATE(B50,F50,D50,UPPER(LEFT(J50,3)),RIGHT(A50,3))</f>
+        <v>GM98SLVBLA018</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B51" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HY</v>
+        <f>LEFT(A51, 2)</f>
+        <v>TY</v>
       </c>
       <c r="C51" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Hyndai</v>
+        <f>VLOOKUP(B51, $B$57:$C$62, 2)</f>
+        <v>Toyota</v>
       </c>
       <c r="D51" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>ELA</v>
+        <f>MID(A51, 5, 3)</f>
+        <v>CAM</v>
       </c>
       <c r="E51" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Elantra</v>
+        <f>VLOOKUP(D51, D$57:E$67, 2)</f>
+        <v>Camery</v>
       </c>
       <c r="F51" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>12</v>
+        <f>MID(A51, 3, 2)</f>
+        <v>00</v>
       </c>
       <c r="G51" s="4">
-        <f t="shared" si="5"/>
-        <v>14</v>
+        <f>IF(26-F51&lt;0, 100-F51+26, 26-F51)</f>
+        <v>26</v>
       </c>
       <c r="H51" s="8">
-        <v>22282</v>
+        <v>85928</v>
       </c>
       <c r="I51" s="8">
-        <f t="shared" si="6"/>
-        <v>1591.5714285714287</v>
+        <f>H51/G51</f>
+        <v>3304.9230769230771</v>
       </c>
       <c r="J51" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L51">
         <v>100000</v>
       </c>
       <c r="M51" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H51&lt;=L51, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N51" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HY12ELABLU050</v>
+        <f>CONCATENATE(B51,F51,D51,UPPER(LEFT(J51,3)),RIGHT(A51,3))</f>
+        <v>TY00CAMGRE022</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="B52" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HY</v>
+        <f>LEFT(A52, 2)</f>
+        <v>TY</v>
       </c>
       <c r="C52" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Hyndai</v>
+        <f>VLOOKUP(B52, $B$57:$C$62, 2)</f>
+        <v>Toyota</v>
       </c>
       <c r="D52" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>ELA</v>
+        <f>MID(A52, 5, 3)</f>
+        <v>CAM</v>
       </c>
       <c r="E52" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Elantra</v>
+        <f>VLOOKUP(D52, D$57:E$67, 2)</f>
+        <v>Camery</v>
       </c>
       <c r="F52" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>13</v>
+        <f>MID(A52, 3, 2)</f>
+        <v>98</v>
       </c>
       <c r="G52" s="4">
-        <f t="shared" si="5"/>
-        <v>13</v>
+        <f>IF(26-F52&lt;0, 100-F52+26, 26-F52)</f>
+        <v>28</v>
       </c>
       <c r="H52" s="8">
-        <v>20223.900000000001</v>
+        <v>93382.6</v>
       </c>
       <c r="I52" s="8">
-        <f t="shared" si="6"/>
-        <v>1555.6846153846154</v>
+        <f>H52/G52</f>
+        <v>3335.0928571428572</v>
       </c>
       <c r="J52" t="s">
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="L52">
         <v>100000</v>
       </c>
       <c r="M52" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(H52&lt;=L52, "Y", "Not Covered")</f>
         <v>Y</v>
       </c>
       <c r="N52" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HY13ELABLA051</v>
+        <f>CONCATENATE(B52,F52,D52,UPPER(LEFT(J52,3)),RIGHT(A52,3))</f>
+        <v>TY98CAMBLA021</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="B53" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HY</v>
+        <f>LEFT(A53, 2)</f>
+        <v>TY</v>
       </c>
       <c r="C53" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Hyndai</v>
+        <f>VLOOKUP(B53, $B$57:$C$62, 2)</f>
+        <v>Toyota</v>
       </c>
       <c r="D53" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>ELA</v>
+        <f>MID(A53, 5, 3)</f>
+        <v>CAM</v>
       </c>
       <c r="E53" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Elantra</v>
+        <f>VLOOKUP(D53, D$57:E$67, 2)</f>
+        <v>Camery</v>
       </c>
       <c r="F53" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>13</v>
+        <f>MID(A53, 3, 2)</f>
+        <v>96</v>
       </c>
       <c r="G53" s="4">
-        <f t="shared" si="5"/>
-        <v>13</v>
+        <f>IF(26-F53&lt;0, 100-F53+26, 26-F53)</f>
+        <v>30</v>
       </c>
       <c r="H53" s="8">
-        <v>22188.5</v>
+        <v>114660.6</v>
       </c>
       <c r="I53" s="8">
-        <f t="shared" si="6"/>
-        <v>1706.8076923076924</v>
+        <f>H53/G53</f>
+        <v>3822.02</v>
       </c>
       <c r="J53" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="L53">
         <v>100000</v>
       </c>
       <c r="M53" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>Y</v>
+        <f>IF(H53&lt;=L53, "Y", "Not Covered")</f>
+        <v>Not Covered</v>
       </c>
       <c r="N53" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v>HY13ELABLU052</v>
+        <f>CONCATENATE(B53,F53,D53,UPPER(LEFT(J53,3)),RIGHT(A53,3))</f>
+        <v>TY96CAMGRE020</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
@@ -4254,18 +8033,32 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B57:C62">
-    <sortCondition ref="B57:B62"/>
+  <autoFilter ref="A1:N1" xr:uid="{BE1BE64A-6E35-46AF-B538-7FFA7D2A357E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N53">
+    <sortCondition ref="H2:H53"/>
   </sortState>
   <conditionalFormatting sqref="M2:M53">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"Not Covered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"Y"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="79" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>